--- a/research/traditional_assets/database/data/ireland/ireland_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_environmental_waste_services.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1782477341389728</v>
+        <v>-0.1585499316005472</v>
       </c>
       <c r="H2">
-        <v>-0.1782477341389728</v>
+        <v>-0.1969904240766074</v>
       </c>
       <c r="I2">
-        <v>-0.2069486404833837</v>
+        <v>-0.2585499316005472</v>
       </c>
       <c r="J2">
-        <v>-0.2069486404833837</v>
+        <v>-0.2585499316005472</v>
       </c>
       <c r="K2">
-        <v>-1.9</v>
+        <v>-0.057</v>
       </c>
       <c r="L2">
-        <v>-0.2870090634441088</v>
+        <v>-0.007797537619699043</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.28</v>
+        <v>1.6</v>
       </c>
       <c r="V2">
-        <v>0.03723404255319149</v>
+        <v>1.081081081081081</v>
       </c>
       <c r="W2">
-        <v>5.9375</v>
+        <v>0.04871794871794873</v>
       </c>
       <c r="X2">
-        <v>0.05985526912867979</v>
+        <v>0.1029872059561056</v>
       </c>
       <c r="Y2">
-        <v>5.87764473087132</v>
-      </c>
-      <c r="Z2">
-        <v>-17.06185567010309</v>
-      </c>
-      <c r="AA2">
-        <v>3.530927835051547</v>
+        <v>-0.0542692572381569</v>
       </c>
       <c r="AB2">
-        <v>0.05892037678014403</v>
-      </c>
-      <c r="AC2">
-        <v>3.472007458271403</v>
+        <v>0.1029872059561056</v>
       </c>
       <c r="AD2">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.004000000000000004</v>
+        <v>-1.6</v>
       </c>
       <c r="AH2">
-        <v>0.03540277065161622</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>-0.3087248322147652</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0005321979776476855</v>
+        <v>13.33333333333332</v>
       </c>
       <c r="AK2">
-        <v>0.003407155025553666</v>
+        <v>-11.42857142857144</v>
       </c>
       <c r="AL2">
-        <v>0.357</v>
+        <v>0.115</v>
       </c>
       <c r="AM2">
-        <v>0.357</v>
+        <v>0.115</v>
       </c>
       <c r="AN2">
-        <v>-0.2090909090909091</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-3.837535014005603</v>
+        <v>-16.43478260869565</v>
       </c>
       <c r="AP2">
-        <v>0.003030303030303033</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="AQ2">
-        <v>-3.837535014005603</v>
+        <v>-16.43478260869565</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1782477341389728</v>
+        <v>-0.1585499316005472</v>
       </c>
       <c r="H3">
-        <v>-0.1782477341389728</v>
+        <v>-0.1969904240766074</v>
       </c>
       <c r="I3">
-        <v>-0.2069486404833837</v>
+        <v>-0.2585499316005472</v>
       </c>
       <c r="J3">
-        <v>-0.2069486404833837</v>
+        <v>-0.2585499316005472</v>
       </c>
       <c r="K3">
-        <v>-1.9</v>
+        <v>-0.057</v>
       </c>
       <c r="L3">
-        <v>-0.2870090634441088</v>
+        <v>-0.007797537619699043</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +743,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.28</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>0.03723404255319149</v>
+        <v>1.081081081081081</v>
       </c>
       <c r="W3">
-        <v>5.9375</v>
+        <v>0.04871794871794873</v>
       </c>
       <c r="X3">
-        <v>0.05985526912867979</v>
+        <v>0.1029872059561056</v>
       </c>
       <c r="Y3">
-        <v>5.87764473087132</v>
-      </c>
-      <c r="Z3">
-        <v>-17.06185567010309</v>
-      </c>
-      <c r="AA3">
-        <v>3.530927835051547</v>
+        <v>-0.0542692572381569</v>
       </c>
       <c r="AB3">
-        <v>0.05892037678014403</v>
-      </c>
-      <c r="AC3">
-        <v>3.472007458271403</v>
+        <v>0.1029872059561056</v>
       </c>
       <c r="AD3">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.004000000000000004</v>
+        <v>-1.6</v>
       </c>
       <c r="AH3">
-        <v>0.03540277065161622</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>-0.3087248322147652</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0005321979776476855</v>
+        <v>13.33333333333332</v>
       </c>
       <c r="AK3">
-        <v>0.003407155025553666</v>
+        <v>-11.42857142857144</v>
       </c>
       <c r="AL3">
-        <v>0.357</v>
+        <v>0.115</v>
       </c>
       <c r="AM3">
-        <v>0.357</v>
+        <v>0.115</v>
       </c>
       <c r="AN3">
-        <v>-0.2090909090909091</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-3.837535014005603</v>
+        <v>-16.43478260869565</v>
       </c>
       <c r="AP3">
-        <v>0.003030303030303033</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="AQ3">
-        <v>-3.837535014005603</v>
+        <v>-16.43478260869565</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_environmental_waste_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="om_koll" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1585499316005472</v>
+        <v>0.06239316239316239</v>
       </c>
       <c r="H2">
-        <v>-0.1969904240766074</v>
+        <v>0.02165242165242165</v>
       </c>
       <c r="I2">
-        <v>-0.2585499316005472</v>
+        <v>0.1314814814814815</v>
       </c>
       <c r="J2">
-        <v>-0.2585499316005472</v>
+        <v>0.06574074074074075</v>
       </c>
       <c r="K2">
-        <v>-0.057</v>
+        <v>-1.21</v>
       </c>
       <c r="L2">
-        <v>-0.007797537619699043</v>
+        <v>-0.1723646723646724</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,22 +629,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>0.18</v>
       </c>
       <c r="V2">
-        <v>1.081081081081081</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="W2">
-        <v>0.04871794871794873</v>
+        <v>-0.6954022988505747</v>
       </c>
       <c r="X2">
-        <v>0.1029872059561056</v>
+        <v>0.08284607652676967</v>
       </c>
       <c r="Y2">
-        <v>-0.0542692572381569</v>
+        <v>-0.7782483753773444</v>
+      </c>
+      <c r="Z2">
+        <v>50.14285714285717</v>
+      </c>
+      <c r="AA2">
+        <v>3.296428571428574</v>
       </c>
       <c r="AB2">
-        <v>0.1029872059561056</v>
+        <v>0.08284607652676967</v>
+      </c>
+      <c r="AC2">
+        <v>3.213582494901804</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -654,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.6</v>
+        <v>-0.18</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -663,28 +674,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>13.33333333333332</v>
+        <v>-0.1578947368421052</v>
       </c>
       <c r="AK2">
-        <v>-11.42857142857144</v>
+        <v>1.855670103092784</v>
       </c>
       <c r="AL2">
-        <v>0.115</v>
+        <v>0.015</v>
       </c>
       <c r="AM2">
-        <v>0.115</v>
+        <v>-0.027</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-16.43478260869565</v>
+        <v>61.53333333333334</v>
       </c>
       <c r="AP2">
-        <v>0.9523809523809524</v>
+        <v>-0.15</v>
       </c>
       <c r="AQ2">
-        <v>-16.43478260869565</v>
+        <v>-34.18518518518518</v>
       </c>
     </row>
     <row r="3">
@@ -704,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1585499316005472</v>
+        <v>0.06239316239316239</v>
       </c>
       <c r="H3">
-        <v>-0.1969904240766074</v>
+        <v>0.02165242165242165</v>
       </c>
       <c r="I3">
-        <v>-0.2585499316005472</v>
+        <v>0.1314814814814815</v>
       </c>
       <c r="J3">
-        <v>-0.2585499316005472</v>
+        <v>0.06574074074074075</v>
       </c>
       <c r="K3">
-        <v>-0.057</v>
+        <v>-1.21</v>
       </c>
       <c r="L3">
-        <v>-0.007797537619699043</v>
+        <v>-0.1723646723646724</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,22 +754,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>0.18</v>
       </c>
       <c r="V3">
-        <v>1.081081081081081</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="W3">
-        <v>0.04871794871794873</v>
+        <v>-0.6954022988505747</v>
       </c>
       <c r="X3">
-        <v>0.1029872059561056</v>
+        <v>0.08284607652676967</v>
       </c>
       <c r="Y3">
-        <v>-0.0542692572381569</v>
+        <v>-0.7782483753773444</v>
+      </c>
+      <c r="Z3">
+        <v>50.14285714285717</v>
+      </c>
+      <c r="AA3">
+        <v>3.296428571428574</v>
       </c>
       <c r="AB3">
-        <v>0.1029872059561056</v>
+        <v>0.08284607652676967</v>
+      </c>
+      <c r="AC3">
+        <v>3.213582494901804</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -770,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.6</v>
+        <v>-0.18</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -779,28 +799,8800 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>13.33333333333332</v>
+        <v>-0.1578947368421052</v>
       </c>
       <c r="AK3">
-        <v>-11.42857142857144</v>
+        <v>1.855670103092784</v>
       </c>
       <c r="AL3">
-        <v>0.115</v>
+        <v>0.015</v>
       </c>
       <c r="AM3">
-        <v>0.115</v>
+        <v>-0.027</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-16.43478260869565</v>
+        <v>61.53333333333334</v>
       </c>
       <c r="AP3">
-        <v>0.9523809523809524</v>
+        <v>-0.15</v>
       </c>
       <c r="AQ3">
-        <v>-16.43478260869565</v>
+        <v>-34.18518518518518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kollect on Demand Holding AB (publ) (OM:KOLL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OM:KOLL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Waste Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>62.4666666666667</v>
+      </c>
+      <c r="F2">
+        <v>16.0406861647456</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1.089</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>1.32</v>
+      </c>
+      <c r="L2">
+        <v>0.048101186219587</v>
+      </c>
+      <c r="M2">
+        <v>1.14</v>
+      </c>
+      <c r="N2">
+        <v>1.17490118621959</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.3068</v>
+      </c>
+      <c r="Q2">
+        <v>0.0828460765267697</v>
+      </c>
+      <c r="R2">
+        <v>0.0777047495565819</v>
+      </c>
+      <c r="S2">
+        <v>0.0855174935376891</v>
+      </c>
+      <c r="T2">
+        <v>0.0391125</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0828460765267697</v>
+      </c>
+      <c r="X2">
+        <v>3.89833745565819</v>
+      </c>
+      <c r="Y2">
+        <v>0.804252110241037</v>
+      </c>
+      <c r="Z2">
+        <v>70.4725911598708</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.0977342783287875</v>
+      </c>
+      <c r="AC2">
+        <v>62.46666666666667</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0.015</v>
+      </c>
+      <c r="AF2">
+        <v>0.263</v>
+      </c>
+      <c r="AG2">
+        <v>1.2</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1.32</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.125</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.8659999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.015</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0.18</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08284607652676967</v>
+      </c>
+      <c r="C2">
+        <v>1.32</v>
+      </c>
+      <c r="D2">
+        <v>1.14</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.18</v>
+      </c>
+      <c r="H2">
+        <v>1.32</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.2</v>
+      </c>
+      <c r="K2">
+        <v>0.263</v>
+      </c>
+      <c r="L2">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.117125</v>
+      </c>
+      <c r="P2">
+        <v>0.8198749999999999</v>
+      </c>
+      <c r="Q2">
+        <v>1.082875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08284607652676967</v>
+      </c>
+      <c r="T2">
+        <v>0.8042521102410373</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.125</v>
+      </c>
+      <c r="W2">
+        <v>0.0391125</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08279414393111123</v>
+      </c>
+      <c r="C3">
+        <v>1.307142167561747</v>
+      </c>
+      <c r="D3">
+        <v>1.140342167561748</v>
+      </c>
+      <c r="E3">
+        <v>0.0132</v>
+      </c>
+      <c r="F3">
+        <v>0.0132</v>
+      </c>
+      <c r="G3">
+        <v>0.18</v>
+      </c>
+      <c r="H3">
+        <v>1.32</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.2</v>
+      </c>
+      <c r="K3">
+        <v>0.263</v>
+      </c>
+      <c r="L3">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.0005900400000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.93640996</v>
+      </c>
+      <c r="O3">
+        <v>0.117051245</v>
+      </c>
+      <c r="P3">
+        <v>0.819358715</v>
+      </c>
+      <c r="Q3">
+        <v>1.082358715</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.0832353726576881</v>
+      </c>
+      <c r="T3">
+        <v>0.8113603990941778</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.125</v>
+      </c>
+      <c r="W3">
+        <v>0.0391125</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1588.027930309809</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08274221133545274</v>
+      </c>
+      <c r="C4">
+        <v>1.294284540586288</v>
+      </c>
+      <c r="D4">
+        <v>1.140684540586288</v>
+      </c>
+      <c r="E4">
+        <v>0.0264</v>
+      </c>
+      <c r="F4">
+        <v>0.0264</v>
+      </c>
+      <c r="G4">
+        <v>0.18</v>
+      </c>
+      <c r="H4">
+        <v>1.32</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.2</v>
+      </c>
+      <c r="K4">
+        <v>0.263</v>
+      </c>
+      <c r="L4">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.00118008</v>
+      </c>
+      <c r="N4">
+        <v>0.9358199199999999</v>
+      </c>
+      <c r="O4">
+        <v>0.11697749</v>
+      </c>
+      <c r="P4">
+        <v>0.8188424299999999</v>
+      </c>
+      <c r="Q4">
+        <v>1.08184243</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08363261360760485</v>
+      </c>
+      <c r="T4">
+        <v>0.81861375506677</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.125</v>
+      </c>
+      <c r="W4">
+        <v>0.0391125</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>794.0139651549046</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08269027873979429</v>
+      </c>
+      <c r="C5">
+        <v>1.281427119258738</v>
+      </c>
+      <c r="D5">
+        <v>1.141027119258738</v>
+      </c>
+      <c r="E5">
+        <v>0.0396</v>
+      </c>
+      <c r="F5">
+        <v>0.0396</v>
+      </c>
+      <c r="G5">
+        <v>0.18</v>
+      </c>
+      <c r="H5">
+        <v>1.32</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.2</v>
+      </c>
+      <c r="K5">
+        <v>0.263</v>
+      </c>
+      <c r="L5">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.00177012</v>
+      </c>
+      <c r="N5">
+        <v>0.93522988</v>
+      </c>
+      <c r="O5">
+        <v>0.116903735</v>
+      </c>
+      <c r="P5">
+        <v>0.818326145</v>
+      </c>
+      <c r="Q5">
+        <v>1.081326145</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08403804509257143</v>
+      </c>
+      <c r="T5">
+        <v>0.826016664770756</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.125</v>
+      </c>
+      <c r="W5">
+        <v>0.0391125</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>529.3426434366031</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08263834614413582</v>
+      </c>
+      <c r="C6">
+        <v>1.26856990376444</v>
+      </c>
+      <c r="D6">
+        <v>1.14136990376444</v>
+      </c>
+      <c r="E6">
+        <v>0.05280000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.05280000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0.18</v>
+      </c>
+      <c r="H6">
+        <v>1.32</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.2</v>
+      </c>
+      <c r="K6">
+        <v>0.263</v>
+      </c>
+      <c r="L6">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M6">
+        <v>0.00236016</v>
+      </c>
+      <c r="N6">
+        <v>0.9346398399999999</v>
+      </c>
+      <c r="O6">
+        <v>0.11682998</v>
+      </c>
+      <c r="P6">
+        <v>0.8178098599999999</v>
+      </c>
+      <c r="Q6">
+        <v>1.08080986</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08445192306680815</v>
+      </c>
+      <c r="T6">
+        <v>0.8335738017602417</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.125</v>
+      </c>
+      <c r="W6">
+        <v>0.0391125</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>397.0069825774523</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08258641354847737</v>
+      </c>
+      <c r="C7">
+        <v>1.255712894288957</v>
+      </c>
+      <c r="D7">
+        <v>1.141712894288957</v>
+      </c>
+      <c r="E7">
+        <v>0.066</v>
+      </c>
+      <c r="F7">
+        <v>0.066</v>
+      </c>
+      <c r="G7">
+        <v>0.18</v>
+      </c>
+      <c r="H7">
+        <v>1.32</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.2</v>
+      </c>
+      <c r="K7">
+        <v>0.263</v>
+      </c>
+      <c r="L7">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M7">
+        <v>0.0029502</v>
+      </c>
+      <c r="N7">
+        <v>0.9340497999999999</v>
+      </c>
+      <c r="O7">
+        <v>0.116756225</v>
+      </c>
+      <c r="P7">
+        <v>0.8172935749999999</v>
+      </c>
+      <c r="Q7">
+        <v>1.080293575</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08487451426155512</v>
+      </c>
+      <c r="T7">
+        <v>0.8412900363705587</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.125</v>
+      </c>
+      <c r="W7">
+        <v>0.0391125</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>317.6055860619618</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0825344809528189</v>
+      </c>
+      <c r="C8">
+        <v>1.242856091018075</v>
+      </c>
+      <c r="D8">
+        <v>1.142056091018075</v>
+      </c>
+      <c r="E8">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="F8">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0.18</v>
+      </c>
+      <c r="H8">
+        <v>1.32</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.2</v>
+      </c>
+      <c r="K8">
+        <v>0.263</v>
+      </c>
+      <c r="L8">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.00354024</v>
+      </c>
+      <c r="N8">
+        <v>0.93345976</v>
+      </c>
+      <c r="O8">
+        <v>0.11668247</v>
+      </c>
+      <c r="P8">
+        <v>0.81677729</v>
+      </c>
+      <c r="Q8">
+        <v>1.07977729</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08530609675831799</v>
+      </c>
+      <c r="T8">
+        <v>0.8491704461853506</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.125</v>
+      </c>
+      <c r="W8">
+        <v>0.0391125</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>264.6713217183016</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08248254835716044</v>
+      </c>
+      <c r="C9">
+        <v>1.229999494137804</v>
+      </c>
+      <c r="D9">
+        <v>1.142399494137804</v>
+      </c>
+      <c r="E9">
+        <v>0.09240000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.09240000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.18</v>
+      </c>
+      <c r="H9">
+        <v>1.32</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.2</v>
+      </c>
+      <c r="K9">
+        <v>0.263</v>
+      </c>
+      <c r="L9">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M9">
+        <v>0.004130280000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.9328697199999999</v>
+      </c>
+      <c r="O9">
+        <v>0.116608715</v>
+      </c>
+      <c r="P9">
+        <v>0.8162610049999999</v>
+      </c>
+      <c r="Q9">
+        <v>1.079261005</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08574696059909725</v>
+      </c>
+      <c r="T9">
+        <v>0.8572203271789551</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.125</v>
+      </c>
+      <c r="W9">
+        <v>0.0391125</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>226.8611329014013</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.082430615761502</v>
+      </c>
+      <c r="C10">
+        <v>1.217143103834379</v>
+      </c>
+      <c r="D10">
+        <v>1.142743103834379</v>
+      </c>
+      <c r="E10">
+        <v>0.1056</v>
+      </c>
+      <c r="F10">
+        <v>0.1056</v>
+      </c>
+      <c r="G10">
+        <v>0.18</v>
+      </c>
+      <c r="H10">
+        <v>1.32</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.2</v>
+      </c>
+      <c r="K10">
+        <v>0.263</v>
+      </c>
+      <c r="L10">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.004720320000000001</v>
+      </c>
+      <c r="N10">
+        <v>0.9322796799999999</v>
+      </c>
+      <c r="O10">
+        <v>0.11653496</v>
+      </c>
+      <c r="P10">
+        <v>0.81574472</v>
+      </c>
+      <c r="Q10">
+        <v>1.07874472</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0861974084364152</v>
+      </c>
+      <c r="T10">
+        <v>0.8654452055854641</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.125</v>
+      </c>
+      <c r="W10">
+        <v>0.0391125</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>198.5034912887261</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08237868316584353</v>
+      </c>
+      <c r="C11">
+        <v>1.204286920294257</v>
+      </c>
+      <c r="D11">
+        <v>1.143086920294257</v>
+      </c>
+      <c r="E11">
+        <v>0.1188</v>
+      </c>
+      <c r="F11">
+        <v>0.1188</v>
+      </c>
+      <c r="G11">
+        <v>0.18</v>
+      </c>
+      <c r="H11">
+        <v>1.32</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.2</v>
+      </c>
+      <c r="K11">
+        <v>0.263</v>
+      </c>
+      <c r="L11">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.005310360000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.93168964</v>
+      </c>
+      <c r="O11">
+        <v>0.116461205</v>
+      </c>
+      <c r="P11">
+        <v>0.815228435</v>
+      </c>
+      <c r="Q11">
+        <v>1.078228435</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08665775622620167</v>
+      </c>
+      <c r="T11">
+        <v>0.8738508505503577</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.125</v>
+      </c>
+      <c r="W11">
+        <v>0.0391125</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>176.447547812201</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08232675057018506</v>
+      </c>
+      <c r="C12">
+        <v>1.191430943704121</v>
+      </c>
+      <c r="D12">
+        <v>1.143430943704121</v>
+      </c>
+      <c r="E12">
+        <v>0.132</v>
+      </c>
+      <c r="F12">
+        <v>0.132</v>
+      </c>
+      <c r="G12">
+        <v>0.18</v>
+      </c>
+      <c r="H12">
+        <v>1.32</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.2</v>
+      </c>
+      <c r="K12">
+        <v>0.263</v>
+      </c>
+      <c r="L12">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M12">
+        <v>0.005900400000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.9310995999999999</v>
+      </c>
+      <c r="O12">
+        <v>0.11638745</v>
+      </c>
+      <c r="P12">
+        <v>0.81471215</v>
+      </c>
+      <c r="Q12">
+        <v>1.07771215</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08712833396687228</v>
+      </c>
+      <c r="T12">
+        <v>0.8824432876255827</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.125</v>
+      </c>
+      <c r="W12">
+        <v>0.0391125</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>158.8027930309809</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0822748179745266</v>
+      </c>
+      <c r="C13">
+        <v>1.178575174250877</v>
+      </c>
+      <c r="D13">
+        <v>1.143775174250877</v>
+      </c>
+      <c r="E13">
+        <v>0.1452</v>
+      </c>
+      <c r="F13">
+        <v>0.1452</v>
+      </c>
+      <c r="G13">
+        <v>0.18</v>
+      </c>
+      <c r="H13">
+        <v>1.32</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.2</v>
+      </c>
+      <c r="K13">
+        <v>0.263</v>
+      </c>
+      <c r="L13">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M13">
+        <v>0.00649044</v>
+      </c>
+      <c r="N13">
+        <v>0.93050956</v>
+      </c>
+      <c r="O13">
+        <v>0.116313695</v>
+      </c>
+      <c r="P13">
+        <v>0.814195865</v>
+      </c>
+      <c r="Q13">
+        <v>1.077195865</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08760948648823214</v>
+      </c>
+      <c r="T13">
+        <v>0.8912288131744079</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.125</v>
+      </c>
+      <c r="W13">
+        <v>0.0391125</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>144.3661754827099</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08222288537886814</v>
+      </c>
+      <c r="C14">
+        <v>1.165719612121659</v>
+      </c>
+      <c r="D14">
+        <v>1.144119612121659</v>
+      </c>
+      <c r="E14">
+        <v>0.1584</v>
+      </c>
+      <c r="F14">
+        <v>0.1584</v>
+      </c>
+      <c r="G14">
+        <v>0.18</v>
+      </c>
+      <c r="H14">
+        <v>1.32</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.2</v>
+      </c>
+      <c r="K14">
+        <v>0.263</v>
+      </c>
+      <c r="L14">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M14">
+        <v>0.007080480000000001</v>
+      </c>
+      <c r="N14">
+        <v>0.9299195199999999</v>
+      </c>
+      <c r="O14">
+        <v>0.11623994</v>
+      </c>
+      <c r="P14">
+        <v>0.8136795799999998</v>
+      </c>
+      <c r="Q14">
+        <v>1.07667958</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08810157429416833</v>
+      </c>
+      <c r="T14">
+        <v>0.9002140097584338</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.125</v>
+      </c>
+      <c r="W14">
+        <v>0.0391125</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>132.3356608591507</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08217095278320966</v>
+      </c>
+      <c r="C15">
+        <v>1.152864257503824</v>
+      </c>
+      <c r="D15">
+        <v>1.144464257503824</v>
+      </c>
+      <c r="E15">
+        <v>0.1716</v>
+      </c>
+      <c r="F15">
+        <v>0.1716</v>
+      </c>
+      <c r="G15">
+        <v>0.18</v>
+      </c>
+      <c r="H15">
+        <v>1.32</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.2</v>
+      </c>
+      <c r="K15">
+        <v>0.263</v>
+      </c>
+      <c r="L15">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M15">
+        <v>0.007670520000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.9293294799999999</v>
+      </c>
+      <c r="O15">
+        <v>0.116166185</v>
+      </c>
+      <c r="P15">
+        <v>0.813163295</v>
+      </c>
+      <c r="Q15">
+        <v>1.076163295</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08860497446345938</v>
+      </c>
+      <c r="T15">
+        <v>0.9094057625857707</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.125</v>
+      </c>
+      <c r="W15">
+        <v>0.0391125</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>122.1559946392161</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.0821190201875512</v>
+      </c>
+      <c r="C16">
+        <v>1.140009110584956</v>
+      </c>
+      <c r="D16">
+        <v>1.144809110584956</v>
+      </c>
+      <c r="E16">
+        <v>0.1848</v>
+      </c>
+      <c r="F16">
+        <v>0.1848</v>
+      </c>
+      <c r="G16">
+        <v>0.18</v>
+      </c>
+      <c r="H16">
+        <v>1.32</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.2</v>
+      </c>
+      <c r="K16">
+        <v>0.263</v>
+      </c>
+      <c r="L16">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M16">
+        <v>0.008260560000000002</v>
+      </c>
+      <c r="N16">
+        <v>0.92873944</v>
+      </c>
+      <c r="O16">
+        <v>0.11609243</v>
+      </c>
+      <c r="P16">
+        <v>0.8126470099999999</v>
+      </c>
+      <c r="Q16">
+        <v>1.07564701</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08912008161343163</v>
+      </c>
+      <c r="T16">
+        <v>0.9188112771067665</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.125</v>
+      </c>
+      <c r="W16">
+        <v>0.0391125</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>113.4305664507007</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08206708759189274</v>
+      </c>
+      <c r="C17">
+        <v>1.127154171552865</v>
+      </c>
+      <c r="D17">
+        <v>1.145154171552865</v>
+      </c>
+      <c r="E17">
+        <v>0.198</v>
+      </c>
+      <c r="F17">
+        <v>0.198</v>
+      </c>
+      <c r="G17">
+        <v>0.18</v>
+      </c>
+      <c r="H17">
+        <v>1.32</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.2</v>
+      </c>
+      <c r="K17">
+        <v>0.263</v>
+      </c>
+      <c r="L17">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M17">
+        <v>0.008850600000000002</v>
+      </c>
+      <c r="N17">
+        <v>0.9281493999999999</v>
+      </c>
+      <c r="O17">
+        <v>0.116018675</v>
+      </c>
+      <c r="P17">
+        <v>0.8121307249999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.075130725</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08964730893163853</v>
+      </c>
+      <c r="T17">
+        <v>0.9284380978517855</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.125</v>
+      </c>
+      <c r="W17">
+        <v>0.0391125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>105.8685286873206</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08201515499623428</v>
+      </c>
+      <c r="C18">
+        <v>1.114299440595586</v>
+      </c>
+      <c r="D18">
+        <v>1.145499440595586</v>
+      </c>
+      <c r="E18">
+        <v>0.2112</v>
+      </c>
+      <c r="F18">
+        <v>0.2112</v>
+      </c>
+      <c r="G18">
+        <v>0.18</v>
+      </c>
+      <c r="H18">
+        <v>1.32</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.2</v>
+      </c>
+      <c r="K18">
+        <v>0.263</v>
+      </c>
+      <c r="L18">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M18">
+        <v>0.009440640000000002</v>
+      </c>
+      <c r="N18">
+        <v>0.9275593599999999</v>
+      </c>
+      <c r="O18">
+        <v>0.11594492</v>
+      </c>
+      <c r="P18">
+        <v>0.8116144399999999</v>
+      </c>
+      <c r="Q18">
+        <v>1.07461444</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09018708928123129</v>
+      </c>
+      <c r="T18">
+        <v>0.9382941286145435</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.125</v>
+      </c>
+      <c r="W18">
+        <v>0.0391125</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>99.25174564436307</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08196322240057582</v>
+      </c>
+      <c r="C19">
+        <v>1.101444917901384</v>
+      </c>
+      <c r="D19">
+        <v>1.145844917901384</v>
+      </c>
+      <c r="E19">
+        <v>0.2244</v>
+      </c>
+      <c r="F19">
+        <v>0.2244</v>
+      </c>
+      <c r="G19">
+        <v>0.18</v>
+      </c>
+      <c r="H19">
+        <v>1.32</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.2</v>
+      </c>
+      <c r="K19">
+        <v>0.263</v>
+      </c>
+      <c r="L19">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M19">
+        <v>0.01003068</v>
+      </c>
+      <c r="N19">
+        <v>0.92696932</v>
+      </c>
+      <c r="O19">
+        <v>0.115871165</v>
+      </c>
+      <c r="P19">
+        <v>0.811098155</v>
+      </c>
+      <c r="Q19">
+        <v>1.074098155</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09073987638623593</v>
+      </c>
+      <c r="T19">
+        <v>0.9483876540944762</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.125</v>
+      </c>
+      <c r="W19">
+        <v>0.0391125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>93.41340766528289</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08191128980491735</v>
+      </c>
+      <c r="C20">
+        <v>1.088590603658749</v>
+      </c>
+      <c r="D20">
+        <v>1.146190603658749</v>
+      </c>
+      <c r="E20">
+        <v>0.2376</v>
+      </c>
+      <c r="F20">
+        <v>0.2376</v>
+      </c>
+      <c r="G20">
+        <v>0.18</v>
+      </c>
+      <c r="H20">
+        <v>1.32</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.2</v>
+      </c>
+      <c r="K20">
+        <v>0.263</v>
+      </c>
+      <c r="L20">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.01062072</v>
+      </c>
+      <c r="N20">
+        <v>0.9263792799999999</v>
+      </c>
+      <c r="O20">
+        <v>0.11579741</v>
+      </c>
+      <c r="P20">
+        <v>0.8105818699999999</v>
+      </c>
+      <c r="Q20">
+        <v>1.07358187</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09130614610355775</v>
+      </c>
+      <c r="T20">
+        <v>0.9587273631226999</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.125</v>
+      </c>
+      <c r="W20">
+        <v>0.0391125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>88.2237739061005</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08185935720925891</v>
+      </c>
+      <c r="C21">
+        <v>1.075736498056397</v>
+      </c>
+      <c r="D21">
+        <v>1.146536498056398</v>
+      </c>
+      <c r="E21">
+        <v>0.2508</v>
+      </c>
+      <c r="F21">
+        <v>0.2508</v>
+      </c>
+      <c r="G21">
+        <v>0.18</v>
+      </c>
+      <c r="H21">
+        <v>1.32</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.2</v>
+      </c>
+      <c r="K21">
+        <v>0.263</v>
+      </c>
+      <c r="L21">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M21">
+        <v>0.01121076</v>
+      </c>
+      <c r="N21">
+        <v>0.92578924</v>
+      </c>
+      <c r="O21">
+        <v>0.115723655</v>
+      </c>
+      <c r="P21">
+        <v>0.8100655849999999</v>
+      </c>
+      <c r="Q21">
+        <v>1.073065585</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09188639778920851</v>
+      </c>
+      <c r="T21">
+        <v>0.9693223736084106</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.125</v>
+      </c>
+      <c r="W21">
+        <v>0.0391125</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>83.5804173847268</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08180742461360044</v>
+      </c>
+      <c r="C22">
+        <v>1.062882601283277</v>
+      </c>
+      <c r="D22">
+        <v>1.146882601283277</v>
+      </c>
+      <c r="E22">
+        <v>0.264</v>
+      </c>
+      <c r="F22">
+        <v>0.264</v>
+      </c>
+      <c r="G22">
+        <v>0.18</v>
+      </c>
+      <c r="H22">
+        <v>1.32</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.2</v>
+      </c>
+      <c r="K22">
+        <v>0.263</v>
+      </c>
+      <c r="L22">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.0118008</v>
+      </c>
+      <c r="N22">
+        <v>0.9251991999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.1156499</v>
+      </c>
+      <c r="P22">
+        <v>0.8095492999999999</v>
+      </c>
+      <c r="Q22">
+        <v>1.0725493</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09248115576700054</v>
+      </c>
+      <c r="T22">
+        <v>0.9801822593562641</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.125</v>
+      </c>
+      <c r="W22">
+        <v>0.0391125</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>79.40139651549045</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08175549201794198</v>
+      </c>
+      <c r="C23">
+        <v>1.05002891352856</v>
+      </c>
+      <c r="D23">
+        <v>1.14722891352856</v>
+      </c>
+      <c r="E23">
+        <v>0.2772</v>
+      </c>
+      <c r="F23">
+        <v>0.2772</v>
+      </c>
+      <c r="G23">
+        <v>0.18</v>
+      </c>
+      <c r="H23">
+        <v>1.32</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.2</v>
+      </c>
+      <c r="K23">
+        <v>0.263</v>
+      </c>
+      <c r="L23">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M23">
+        <v>0.01239084</v>
+      </c>
+      <c r="N23">
+        <v>0.9246091599999999</v>
+      </c>
+      <c r="O23">
+        <v>0.115576145</v>
+      </c>
+      <c r="P23">
+        <v>0.8090330149999999</v>
+      </c>
+      <c r="Q23">
+        <v>1.072033015</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.0930909709087873</v>
+      </c>
+      <c r="T23">
+        <v>0.991317078920519</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.125</v>
+      </c>
+      <c r="W23">
+        <v>0.0391125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>75.62037763380043</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08170355942228349</v>
+      </c>
+      <c r="C24">
+        <v>1.037175434981651</v>
+      </c>
+      <c r="D24">
+        <v>1.147575434981651</v>
+      </c>
+      <c r="E24">
+        <v>0.2904</v>
+      </c>
+      <c r="F24">
+        <v>0.2904</v>
+      </c>
+      <c r="G24">
+        <v>0.18</v>
+      </c>
+      <c r="H24">
+        <v>1.32</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.2</v>
+      </c>
+      <c r="K24">
+        <v>0.263</v>
+      </c>
+      <c r="L24">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M24">
+        <v>0.01298088</v>
+      </c>
+      <c r="N24">
+        <v>0.92401912</v>
+      </c>
+      <c r="O24">
+        <v>0.11550239</v>
+      </c>
+      <c r="P24">
+        <v>0.80851673</v>
+      </c>
+      <c r="Q24">
+        <v>1.07151673</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.0937164223362609</v>
+      </c>
+      <c r="T24">
+        <v>1.002737406678729</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.125</v>
+      </c>
+      <c r="W24">
+        <v>0.0391125</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>72.18308774135497</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08165162682662505</v>
+      </c>
+      <c r="C25">
+        <v>1.024322165832179</v>
+      </c>
+      <c r="D25">
+        <v>1.147922165832179</v>
+      </c>
+      <c r="E25">
+        <v>0.3036</v>
+      </c>
+      <c r="F25">
+        <v>0.3036</v>
+      </c>
+      <c r="G25">
+        <v>0.18</v>
+      </c>
+      <c r="H25">
+        <v>1.32</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.2</v>
+      </c>
+      <c r="K25">
+        <v>0.263</v>
+      </c>
+      <c r="L25">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M25">
+        <v>0.01357092</v>
+      </c>
+      <c r="N25">
+        <v>0.9234290799999999</v>
+      </c>
+      <c r="O25">
+        <v>0.115428635</v>
+      </c>
+      <c r="P25">
+        <v>0.8080004449999999</v>
+      </c>
+      <c r="Q25">
+        <v>1.071000445</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.0943581192553572</v>
+      </c>
+      <c r="T25">
+        <v>1.014454366326763</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.125</v>
+      </c>
+      <c r="W25">
+        <v>0.0391125</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>69.04469262216561</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08159969423096658</v>
+      </c>
+      <c r="C26">
+        <v>1.011469106270007</v>
+      </c>
+      <c r="D26">
+        <v>1.148269106270007</v>
+      </c>
+      <c r="E26">
+        <v>0.3168</v>
+      </c>
+      <c r="F26">
+        <v>0.3168</v>
+      </c>
+      <c r="G26">
+        <v>0.18</v>
+      </c>
+      <c r="H26">
+        <v>1.32</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.2</v>
+      </c>
+      <c r="K26">
+        <v>0.263</v>
+      </c>
+      <c r="L26">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M26">
+        <v>0.01416096</v>
+      </c>
+      <c r="N26">
+        <v>0.9228390399999999</v>
+      </c>
+      <c r="O26">
+        <v>0.11535488</v>
+      </c>
+      <c r="P26">
+        <v>0.80748416</v>
+      </c>
+      <c r="Q26">
+        <v>1.07048416</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09501670293548234</v>
+      </c>
+      <c r="T26">
+        <v>1.026479667018166</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.125</v>
+      </c>
+      <c r="W26">
+        <v>0.0391125</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>66.16783042957539</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08154776163530811</v>
+      </c>
+      <c r="C27">
+        <v>0.9986162564852239</v>
+      </c>
+      <c r="D27">
+        <v>1.148616256485224</v>
+      </c>
+      <c r="E27">
+        <v>0.33</v>
+      </c>
+      <c r="F27">
+        <v>0.33</v>
+      </c>
+      <c r="G27">
+        <v>0.18</v>
+      </c>
+      <c r="H27">
+        <v>1.32</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.2</v>
+      </c>
+      <c r="K27">
+        <v>0.263</v>
+      </c>
+      <c r="L27">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M27">
+        <v>0.014751</v>
+      </c>
+      <c r="N27">
+        <v>0.922249</v>
+      </c>
+      <c r="O27">
+        <v>0.115281125</v>
+      </c>
+      <c r="P27">
+        <v>0.806967875</v>
+      </c>
+      <c r="Q27">
+        <v>1.069967875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09569284884707749</v>
+      </c>
+      <c r="T27">
+        <v>1.038825642394673</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.125</v>
+      </c>
+      <c r="W27">
+        <v>0.0391125</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>63.52111721239237</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08149582903964968</v>
+      </c>
+      <c r="C28">
+        <v>0.98576361666815</v>
+      </c>
+      <c r="D28">
+        <v>1.14896361666815</v>
+      </c>
+      <c r="E28">
+        <v>0.3432</v>
+      </c>
+      <c r="F28">
+        <v>0.3432</v>
+      </c>
+      <c r="G28">
+        <v>0.18</v>
+      </c>
+      <c r="H28">
+        <v>1.32</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.2</v>
+      </c>
+      <c r="K28">
+        <v>0.263</v>
+      </c>
+      <c r="L28">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M28">
+        <v>0.01534104</v>
+      </c>
+      <c r="N28">
+        <v>0.9216589599999999</v>
+      </c>
+      <c r="O28">
+        <v>0.11520737</v>
+      </c>
+      <c r="P28">
+        <v>0.8064515899999999</v>
+      </c>
+      <c r="Q28">
+        <v>1.06945159</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09638726897249955</v>
+      </c>
+      <c r="T28">
+        <v>1.051505292781356</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.125</v>
+      </c>
+      <c r="W28">
+        <v>0.0391125</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>61.07799731960804</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08144389644399119</v>
+      </c>
+      <c r="C29">
+        <v>0.9729111870093368</v>
+      </c>
+      <c r="D29">
+        <v>1.149311187009337</v>
+      </c>
+      <c r="E29">
+        <v>0.3564000000000001</v>
+      </c>
+      <c r="F29">
+        <v>0.3564000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.18</v>
+      </c>
+      <c r="H29">
+        <v>1.32</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.2</v>
+      </c>
+      <c r="K29">
+        <v>0.263</v>
+      </c>
+      <c r="L29">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M29">
+        <v>0.01593108</v>
+      </c>
+      <c r="N29">
+        <v>0.92106892</v>
+      </c>
+      <c r="O29">
+        <v>0.115133615</v>
+      </c>
+      <c r="P29">
+        <v>0.805935305</v>
+      </c>
+      <c r="Q29">
+        <v>1.068935305</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09710071430683725</v>
+      </c>
+      <c r="T29">
+        <v>1.064532330849866</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.125</v>
+      </c>
+      <c r="W29">
+        <v>0.0391125</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>58.81584927073367</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08139196384833274</v>
+      </c>
+      <c r="C30">
+        <v>0.9600589676995647</v>
+      </c>
+      <c r="D30">
+        <v>1.149658967699565</v>
+      </c>
+      <c r="E30">
+        <v>0.3696</v>
+      </c>
+      <c r="F30">
+        <v>0.3696</v>
+      </c>
+      <c r="G30">
+        <v>0.18</v>
+      </c>
+      <c r="H30">
+        <v>1.32</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.2</v>
+      </c>
+      <c r="K30">
+        <v>0.263</v>
+      </c>
+      <c r="L30">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M30">
+        <v>0.01652112</v>
+      </c>
+      <c r="N30">
+        <v>0.9204788799999999</v>
+      </c>
+      <c r="O30">
+        <v>0.11505986</v>
+      </c>
+      <c r="P30">
+        <v>0.8054190199999999</v>
+      </c>
+      <c r="Q30">
+        <v>1.06841902</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.0978339775671288</v>
+      </c>
+      <c r="T30">
+        <v>1.077921231086946</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.125</v>
+      </c>
+      <c r="W30">
+        <v>0.0391125</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>56.71528322535032</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08134003125267426</v>
+      </c>
+      <c r="C31">
+        <v>0.947206958929846</v>
+      </c>
+      <c r="D31">
+        <v>1.150006958929846</v>
+      </c>
+      <c r="E31">
+        <v>0.3828</v>
+      </c>
+      <c r="F31">
+        <v>0.3828</v>
+      </c>
+      <c r="G31">
+        <v>0.18</v>
+      </c>
+      <c r="H31">
+        <v>1.32</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.2</v>
+      </c>
+      <c r="K31">
+        <v>0.263</v>
+      </c>
+      <c r="L31">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M31">
+        <v>0.01711116</v>
+      </c>
+      <c r="N31">
+        <v>0.9198888399999999</v>
+      </c>
+      <c r="O31">
+        <v>0.114986105</v>
+      </c>
+      <c r="P31">
+        <v>0.804902735</v>
+      </c>
+      <c r="Q31">
+        <v>1.067902735</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09858789613052715</v>
+      </c>
+      <c r="T31">
+        <v>1.09168728344338</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.125</v>
+      </c>
+      <c r="W31">
+        <v>0.0391125</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>54.75958380378653</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08128809865701581</v>
+      </c>
+      <c r="C32">
+        <v>0.9343551608914241</v>
+      </c>
+      <c r="D32">
+        <v>1.150355160891424</v>
+      </c>
+      <c r="E32">
+        <v>0.396</v>
+      </c>
+      <c r="F32">
+        <v>0.396</v>
+      </c>
+      <c r="G32">
+        <v>0.18</v>
+      </c>
+      <c r="H32">
+        <v>1.32</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.2</v>
+      </c>
+      <c r="K32">
+        <v>0.263</v>
+      </c>
+      <c r="L32">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.0177012</v>
+      </c>
+      <c r="N32">
+        <v>0.9192988</v>
+      </c>
+      <c r="O32">
+        <v>0.11491235</v>
+      </c>
+      <c r="P32">
+        <v>0.80438645</v>
+      </c>
+      <c r="Q32">
+        <v>1.06738645</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09936335522430831</v>
+      </c>
+      <c r="T32">
+        <v>1.105846651581426</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.125</v>
+      </c>
+      <c r="W32">
+        <v>0.0391125</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>52.9342643436603</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08123616606135733</v>
+      </c>
+      <c r="C33">
+        <v>0.9215035737757746</v>
+      </c>
+      <c r="D33">
+        <v>1.150703573775775</v>
+      </c>
+      <c r="E33">
+        <v>0.4092</v>
+      </c>
+      <c r="F33">
+        <v>0.4092</v>
+      </c>
+      <c r="G33">
+        <v>0.18</v>
+      </c>
+      <c r="H33">
+        <v>1.32</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.2</v>
+      </c>
+      <c r="K33">
+        <v>0.263</v>
+      </c>
+      <c r="L33">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M33">
+        <v>0.01829124</v>
+      </c>
+      <c r="N33">
+        <v>0.9187087599999999</v>
+      </c>
+      <c r="O33">
+        <v>0.114838595</v>
+      </c>
+      <c r="P33">
+        <v>0.803870165</v>
+      </c>
+      <c r="Q33">
+        <v>1.066870165</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1001612913932715</v>
+      </c>
+      <c r="T33">
+        <v>1.120416436187242</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.125</v>
+      </c>
+      <c r="W33">
+        <v>0.0391125</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>51.22670742934869</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08118423346569889</v>
+      </c>
+      <c r="C34">
+        <v>0.908652197774604</v>
+      </c>
+      <c r="D34">
+        <v>1.151052197774604</v>
+      </c>
+      <c r="E34">
+        <v>0.4224000000000001</v>
+      </c>
+      <c r="F34">
+        <v>0.4224000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.18</v>
+      </c>
+      <c r="H34">
+        <v>1.32</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.2</v>
+      </c>
+      <c r="K34">
+        <v>0.263</v>
+      </c>
+      <c r="L34">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M34">
+        <v>0.01888128</v>
+      </c>
+      <c r="N34">
+        <v>0.9181187199999999</v>
+      </c>
+      <c r="O34">
+        <v>0.11476484</v>
+      </c>
+      <c r="P34">
+        <v>0.80335388</v>
+      </c>
+      <c r="Q34">
+        <v>1.06635388</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1009826962730866</v>
+      </c>
+      <c r="T34">
+        <v>1.1354147438697</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.125</v>
+      </c>
+      <c r="W34">
+        <v>0.0391125</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>49.62587282218153</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08113230087004043</v>
+      </c>
+      <c r="C35">
+        <v>0.8958010330798531</v>
+      </c>
+      <c r="D35">
+        <v>1.151401033079853</v>
+      </c>
+      <c r="E35">
+        <v>0.4356</v>
+      </c>
+      <c r="F35">
+        <v>0.4356</v>
+      </c>
+      <c r="G35">
+        <v>0.18</v>
+      </c>
+      <c r="H35">
+        <v>1.32</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.2</v>
+      </c>
+      <c r="K35">
+        <v>0.263</v>
+      </c>
+      <c r="L35">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M35">
+        <v>0.01947132</v>
+      </c>
+      <c r="N35">
+        <v>0.91752868</v>
+      </c>
+      <c r="O35">
+        <v>0.114691085</v>
+      </c>
+      <c r="P35">
+        <v>0.802837595</v>
+      </c>
+      <c r="Q35">
+        <v>1.065837595</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1018286207015529</v>
+      </c>
+      <c r="T35">
+        <v>1.150860762229245</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.125</v>
+      </c>
+      <c r="W35">
+        <v>0.0391125</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>48.12205849423664</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08108036827438195</v>
+      </c>
+      <c r="C36">
+        <v>0.8829500798836938</v>
+      </c>
+      <c r="D36">
+        <v>1.151750079883694</v>
+      </c>
+      <c r="E36">
+        <v>0.4488</v>
+      </c>
+      <c r="F36">
+        <v>0.4488</v>
+      </c>
+      <c r="G36">
+        <v>0.18</v>
+      </c>
+      <c r="H36">
+        <v>1.32</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.2</v>
+      </c>
+      <c r="K36">
+        <v>0.263</v>
+      </c>
+      <c r="L36">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M36">
+        <v>0.02006136</v>
+      </c>
+      <c r="N36">
+        <v>0.9169386399999999</v>
+      </c>
+      <c r="O36">
+        <v>0.11461733</v>
+      </c>
+      <c r="P36">
+        <v>0.80232131</v>
+      </c>
+      <c r="Q36">
+        <v>1.06532131</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.102700179203609</v>
+      </c>
+      <c r="T36">
+        <v>1.166774841751202</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.125</v>
+      </c>
+      <c r="W36">
+        <v>0.0391125</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>46.70670383264144</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08102843567872349</v>
+      </c>
+      <c r="C37">
+        <v>0.870099338378531</v>
+      </c>
+      <c r="D37">
+        <v>1.152099338378531</v>
+      </c>
+      <c r="E37">
+        <v>0.4620000000000001</v>
+      </c>
+      <c r="F37">
+        <v>0.4620000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.18</v>
+      </c>
+      <c r="H37">
+        <v>1.32</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.2</v>
+      </c>
+      <c r="K37">
+        <v>0.263</v>
+      </c>
+      <c r="L37">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M37">
+        <v>0.0206514</v>
+      </c>
+      <c r="N37">
+        <v>0.9163486</v>
+      </c>
+      <c r="O37">
+        <v>0.114543575</v>
+      </c>
+      <c r="P37">
+        <v>0.8018050249999999</v>
+      </c>
+      <c r="Q37">
+        <v>1.064805025</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1035985548903438</v>
+      </c>
+      <c r="T37">
+        <v>1.183178585258449</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.125</v>
+      </c>
+      <c r="W37">
+        <v>0.0391125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>45.37222658028026</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08097650308306505</v>
+      </c>
+      <c r="C38">
+        <v>0.8572488087570043</v>
+      </c>
+      <c r="D38">
+        <v>1.152448808757004</v>
+      </c>
+      <c r="E38">
+        <v>0.4752</v>
+      </c>
+      <c r="F38">
+        <v>0.4752</v>
+      </c>
+      <c r="G38">
+        <v>0.18</v>
+      </c>
+      <c r="H38">
+        <v>1.32</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.2</v>
+      </c>
+      <c r="K38">
+        <v>0.263</v>
+      </c>
+      <c r="L38">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M38">
+        <v>0.02124144</v>
+      </c>
+      <c r="N38">
+        <v>0.9157585599999999</v>
+      </c>
+      <c r="O38">
+        <v>0.11446982</v>
+      </c>
+      <c r="P38">
+        <v>0.8012887399999999</v>
+      </c>
+      <c r="Q38">
+        <v>1.06428874</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1045250048172891</v>
+      </c>
+      <c r="T38">
+        <v>1.200094945750298</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.125</v>
+      </c>
+      <c r="W38">
+        <v>0.0391125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>44.11188695305025</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08092457048740657</v>
+      </c>
+      <c r="C39">
+        <v>0.8443984912119866</v>
+      </c>
+      <c r="D39">
+        <v>1.152798491211987</v>
+      </c>
+      <c r="E39">
+        <v>0.4884</v>
+      </c>
+      <c r="F39">
+        <v>0.4884</v>
+      </c>
+      <c r="G39">
+        <v>0.18</v>
+      </c>
+      <c r="H39">
+        <v>1.32</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.2</v>
+      </c>
+      <c r="K39">
+        <v>0.263</v>
+      </c>
+      <c r="L39">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M39">
+        <v>0.02183148</v>
+      </c>
+      <c r="N39">
+        <v>0.9151685199999999</v>
+      </c>
+      <c r="O39">
+        <v>0.114396065</v>
+      </c>
+      <c r="P39">
+        <v>0.8007724549999999</v>
+      </c>
+      <c r="Q39">
+        <v>1.063772455</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1054808658530263</v>
+      </c>
+      <c r="T39">
+        <v>1.217548333559348</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.125</v>
+      </c>
+      <c r="W39">
+        <v>0.0391125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>42.91967379215701</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08087263789174812</v>
+      </c>
+      <c r="C40">
+        <v>0.831548385936584</v>
+      </c>
+      <c r="D40">
+        <v>1.153148385936584</v>
+      </c>
+      <c r="E40">
+        <v>0.5016</v>
+      </c>
+      <c r="F40">
+        <v>0.5016</v>
+      </c>
+      <c r="G40">
+        <v>0.18</v>
+      </c>
+      <c r="H40">
+        <v>1.32</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.2</v>
+      </c>
+      <c r="K40">
+        <v>0.263</v>
+      </c>
+      <c r="L40">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M40">
+        <v>0.02242152</v>
+      </c>
+      <c r="N40">
+        <v>0.91457848</v>
+      </c>
+      <c r="O40">
+        <v>0.11432231</v>
+      </c>
+      <c r="P40">
+        <v>0.8002561699999999</v>
+      </c>
+      <c r="Q40">
+        <v>1.06325617</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1064675611157228</v>
+      </c>
+      <c r="T40">
+        <v>1.235564733878368</v>
+      </c>
+      <c r="U40">
+        <v>0.0447</v>
+      </c>
+      <c r="V40">
+        <v>0.125</v>
+      </c>
+      <c r="W40">
+        <v>0.0391125</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>41.7902086923634</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08082070529608965</v>
+      </c>
+      <c r="C41">
+        <v>0.8186984931241387</v>
+      </c>
+      <c r="D41">
+        <v>1.153498493124139</v>
+      </c>
+      <c r="E41">
+        <v>0.5148</v>
+      </c>
+      <c r="F41">
+        <v>0.5148</v>
+      </c>
+      <c r="G41">
+        <v>0.18</v>
+      </c>
+      <c r="H41">
+        <v>1.32</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.2</v>
+      </c>
+      <c r="K41">
+        <v>0.263</v>
+      </c>
+      <c r="L41">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M41">
+        <v>0.02301156</v>
+      </c>
+      <c r="N41">
+        <v>0.9139884399999999</v>
+      </c>
+      <c r="O41">
+        <v>0.114248555</v>
+      </c>
+      <c r="P41">
+        <v>0.7997398849999999</v>
+      </c>
+      <c r="Q41">
+        <v>1.062739885</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1074866070427699</v>
+      </c>
+      <c r="T41">
+        <v>1.254171835847191</v>
+      </c>
+      <c r="U41">
+        <v>0.0447</v>
+      </c>
+      <c r="V41">
+        <v>0.125</v>
+      </c>
+      <c r="W41">
+        <v>0.0391125</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>40.7186648797387</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0807687727004312</v>
+      </c>
+      <c r="C42">
+        <v>0.8058488129682264</v>
+      </c>
+      <c r="D42">
+        <v>1.153848812968227</v>
+      </c>
+      <c r="E42">
+        <v>0.528</v>
+      </c>
+      <c r="F42">
+        <v>0.528</v>
+      </c>
+      <c r="G42">
+        <v>0.18</v>
+      </c>
+      <c r="H42">
+        <v>1.32</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.2</v>
+      </c>
+      <c r="K42">
+        <v>0.263</v>
+      </c>
+      <c r="L42">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M42">
+        <v>0.0236016</v>
+      </c>
+      <c r="N42">
+        <v>0.9133983999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.1141748</v>
+      </c>
+      <c r="P42">
+        <v>0.7992235999999999</v>
+      </c>
+      <c r="Q42">
+        <v>1.0622236</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1085396211673853</v>
+      </c>
+      <c r="T42">
+        <v>1.273399174548309</v>
+      </c>
+      <c r="U42">
+        <v>0.0447</v>
+      </c>
+      <c r="V42">
+        <v>0.125</v>
+      </c>
+      <c r="W42">
+        <v>0.0391125</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>39.70069825774523</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08071684010477273</v>
+      </c>
+      <c r="C43">
+        <v>0.7929993456626591</v>
+      </c>
+      <c r="D43">
+        <v>1.154199345662659</v>
+      </c>
+      <c r="E43">
+        <v>0.5412</v>
+      </c>
+      <c r="F43">
+        <v>0.5412</v>
+      </c>
+      <c r="G43">
+        <v>0.18</v>
+      </c>
+      <c r="H43">
+        <v>1.32</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.2</v>
+      </c>
+      <c r="K43">
+        <v>0.263</v>
+      </c>
+      <c r="L43">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.02419164</v>
+      </c>
+      <c r="N43">
+        <v>0.91280836</v>
+      </c>
+      <c r="O43">
+        <v>0.114101045</v>
+      </c>
+      <c r="P43">
+        <v>0.798707315</v>
+      </c>
+      <c r="Q43">
+        <v>1.061707315</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1096283306860555</v>
+      </c>
+      <c r="T43">
+        <v>1.293278287442685</v>
+      </c>
+      <c r="U43">
+        <v>0.0447</v>
+      </c>
+      <c r="V43">
+        <v>0.125</v>
+      </c>
+      <c r="W43">
+        <v>0.0391125</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>38.73238854414169</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08066490750911427</v>
+      </c>
+      <c r="C44">
+        <v>0.7801500914014838</v>
+      </c>
+      <c r="D44">
+        <v>1.154550091401484</v>
+      </c>
+      <c r="E44">
+        <v>0.5544</v>
+      </c>
+      <c r="F44">
+        <v>0.5544</v>
+      </c>
+      <c r="G44">
+        <v>0.18</v>
+      </c>
+      <c r="H44">
+        <v>1.32</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.2</v>
+      </c>
+      <c r="K44">
+        <v>0.263</v>
+      </c>
+      <c r="L44">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M44">
+        <v>0.02478168</v>
+      </c>
+      <c r="N44">
+        <v>0.9122183199999999</v>
+      </c>
+      <c r="O44">
+        <v>0.11402729</v>
+      </c>
+      <c r="P44">
+        <v>0.7981910299999999</v>
+      </c>
+      <c r="Q44">
+        <v>1.06119103</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.110754581912266</v>
+      </c>
+      <c r="T44">
+        <v>1.313842886988591</v>
+      </c>
+      <c r="U44">
+        <v>0.0447</v>
+      </c>
+      <c r="V44">
+        <v>0.125</v>
+      </c>
+      <c r="W44">
+        <v>0.0391125</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>37.81018881690022</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08061297491345581</v>
+      </c>
+      <c r="C45">
+        <v>0.7673010503789833</v>
+      </c>
+      <c r="D45">
+        <v>1.154901050378983</v>
+      </c>
+      <c r="E45">
+        <v>0.5676</v>
+      </c>
+      <c r="F45">
+        <v>0.5676</v>
+      </c>
+      <c r="G45">
+        <v>0.18</v>
+      </c>
+      <c r="H45">
+        <v>1.32</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.2</v>
+      </c>
+      <c r="K45">
+        <v>0.263</v>
+      </c>
+      <c r="L45">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M45">
+        <v>0.02537172</v>
+      </c>
+      <c r="N45">
+        <v>0.91162828</v>
+      </c>
+      <c r="O45">
+        <v>0.113953535</v>
+      </c>
+      <c r="P45">
+        <v>0.7976747449999999</v>
+      </c>
+      <c r="Q45">
+        <v>1.060674745</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1119203507253611</v>
+      </c>
+      <c r="T45">
+        <v>1.335129051430845</v>
+      </c>
+      <c r="U45">
+        <v>0.0447</v>
+      </c>
+      <c r="V45">
+        <v>0.125</v>
+      </c>
+      <c r="W45">
+        <v>0.0391125</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>36.93088210022812</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08056104231779736</v>
+      </c>
+      <c r="C46">
+        <v>0.7544522227896775</v>
+      </c>
+      <c r="D46">
+        <v>1.155252222789678</v>
+      </c>
+      <c r="E46">
+        <v>0.5808</v>
+      </c>
+      <c r="F46">
+        <v>0.5808</v>
+      </c>
+      <c r="G46">
+        <v>0.18</v>
+      </c>
+      <c r="H46">
+        <v>1.32</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.2</v>
+      </c>
+      <c r="K46">
+        <v>0.263</v>
+      </c>
+      <c r="L46">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M46">
+        <v>0.02596176</v>
+      </c>
+      <c r="N46">
+        <v>0.9110382399999999</v>
+      </c>
+      <c r="O46">
+        <v>0.11387978</v>
+      </c>
+      <c r="P46">
+        <v>0.7971584599999999</v>
+      </c>
+      <c r="Q46">
+        <v>1.06015846</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1131277541389238</v>
+      </c>
+      <c r="T46">
+        <v>1.35717543603175</v>
+      </c>
+      <c r="U46">
+        <v>0.0447</v>
+      </c>
+      <c r="V46">
+        <v>0.125</v>
+      </c>
+      <c r="W46">
+        <v>0.0391125</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>36.09154387067748</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.0805091097221389</v>
+      </c>
+      <c r="C47">
+        <v>0.7416036088283218</v>
+      </c>
+      <c r="D47">
+        <v>1.155603608828322</v>
+      </c>
+      <c r="E47">
+        <v>0.5940000000000001</v>
+      </c>
+      <c r="F47">
+        <v>0.5940000000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.18</v>
+      </c>
+      <c r="H47">
+        <v>1.32</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.2</v>
+      </c>
+      <c r="K47">
+        <v>0.263</v>
+      </c>
+      <c r="L47">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M47">
+        <v>0.02655180000000001</v>
+      </c>
+      <c r="N47">
+        <v>0.9104481999999999</v>
+      </c>
+      <c r="O47">
+        <v>0.113806025</v>
+      </c>
+      <c r="P47">
+        <v>0.7966421749999999</v>
+      </c>
+      <c r="Q47">
+        <v>1.059642175</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1143790631311616</v>
+      </c>
+      <c r="T47">
+        <v>1.380023507345416</v>
+      </c>
+      <c r="U47">
+        <v>0.0447</v>
+      </c>
+      <c r="V47">
+        <v>0.125</v>
+      </c>
+      <c r="W47">
+        <v>0.0391125</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>35.2895095624402</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08045717712648043</v>
+      </c>
+      <c r="C48">
+        <v>0.7287552086899097</v>
+      </c>
+      <c r="D48">
+        <v>1.15595520868991</v>
+      </c>
+      <c r="E48">
+        <v>0.6072000000000001</v>
+      </c>
+      <c r="F48">
+        <v>0.6072000000000001</v>
+      </c>
+      <c r="G48">
+        <v>0.18</v>
+      </c>
+      <c r="H48">
+        <v>1.32</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.2</v>
+      </c>
+      <c r="K48">
+        <v>0.263</v>
+      </c>
+      <c r="L48">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M48">
+        <v>0.02714184</v>
+      </c>
+      <c r="N48">
+        <v>0.90985816</v>
+      </c>
+      <c r="O48">
+        <v>0.11373227</v>
+      </c>
+      <c r="P48">
+        <v>0.79612589</v>
+      </c>
+      <c r="Q48">
+        <v>1.05912589</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1156767169008897</v>
+      </c>
+      <c r="T48">
+        <v>1.403717803522551</v>
+      </c>
+      <c r="U48">
+        <v>0.0447</v>
+      </c>
+      <c r="V48">
+        <v>0.125</v>
+      </c>
+      <c r="W48">
+        <v>0.0391125</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>34.52234631108281</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08040524453082197</v>
+      </c>
+      <c r="C49">
+        <v>0.7159070225696713</v>
+      </c>
+      <c r="D49">
+        <v>1.156307022569671</v>
+      </c>
+      <c r="E49">
+        <v>0.6204000000000001</v>
+      </c>
+      <c r="F49">
+        <v>0.6204000000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.18</v>
+      </c>
+      <c r="H49">
+        <v>1.32</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.2</v>
+      </c>
+      <c r="K49">
+        <v>0.263</v>
+      </c>
+      <c r="L49">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M49">
+        <v>0.02773188</v>
+      </c>
+      <c r="N49">
+        <v>0.9092681199999999</v>
+      </c>
+      <c r="O49">
+        <v>0.113658515</v>
+      </c>
+      <c r="P49">
+        <v>0.7956096049999999</v>
+      </c>
+      <c r="Q49">
+        <v>1.058609605</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1170233387373999</v>
+      </c>
+      <c r="T49">
+        <v>1.428306224083729</v>
+      </c>
+      <c r="U49">
+        <v>0.0447</v>
+      </c>
+      <c r="V49">
+        <v>0.125</v>
+      </c>
+      <c r="W49">
+        <v>0.0391125</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>33.78782830446402</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08035331193516349</v>
+      </c>
+      <c r="C50">
+        <v>0.7030590506630753</v>
+      </c>
+      <c r="D50">
+        <v>1.156659050663075</v>
+      </c>
+      <c r="E50">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="F50">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="G50">
+        <v>0.18</v>
+      </c>
+      <c r="H50">
+        <v>1.32</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.2</v>
+      </c>
+      <c r="K50">
+        <v>0.263</v>
+      </c>
+      <c r="L50">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M50">
+        <v>0.02832192</v>
+      </c>
+      <c r="N50">
+        <v>0.9086780799999999</v>
+      </c>
+      <c r="O50">
+        <v>0.11358476</v>
+      </c>
+      <c r="P50">
+        <v>0.79509332</v>
+      </c>
+      <c r="Q50">
+        <v>1.05809332</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1184217537214683</v>
+      </c>
+      <c r="T50">
+        <v>1.453840353128029</v>
+      </c>
+      <c r="U50">
+        <v>0.0447</v>
+      </c>
+      <c r="V50">
+        <v>0.125</v>
+      </c>
+      <c r="W50">
+        <v>0.0391125</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>33.08391521478769</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08030137933950504</v>
+      </c>
+      <c r="C51">
+        <v>0.6902112931658275</v>
+      </c>
+      <c r="D51">
+        <v>1.157011293165828</v>
+      </c>
+      <c r="E51">
+        <v>0.6468</v>
+      </c>
+      <c r="F51">
+        <v>0.6468</v>
+      </c>
+      <c r="G51">
+        <v>0.18</v>
+      </c>
+      <c r="H51">
+        <v>1.32</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.2</v>
+      </c>
+      <c r="K51">
+        <v>0.263</v>
+      </c>
+      <c r="L51">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M51">
+        <v>0.02891196</v>
+      </c>
+      <c r="N51">
+        <v>0.90808804</v>
+      </c>
+      <c r="O51">
+        <v>0.113511005</v>
+      </c>
+      <c r="P51">
+        <v>0.794577035</v>
+      </c>
+      <c r="Q51">
+        <v>1.057577035</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1198750085088334</v>
+      </c>
+      <c r="T51">
+        <v>1.480375820566223</v>
+      </c>
+      <c r="U51">
+        <v>0.0447</v>
+      </c>
+      <c r="V51">
+        <v>0.125</v>
+      </c>
+      <c r="W51">
+        <v>0.0391125</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>32.40873327162876</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08024944674384657</v>
+      </c>
+      <c r="C52">
+        <v>0.6773637502738731</v>
+      </c>
+      <c r="D52">
+        <v>1.157363750273873</v>
+      </c>
+      <c r="E52">
+        <v>0.66</v>
+      </c>
+      <c r="F52">
+        <v>0.66</v>
+      </c>
+      <c r="G52">
+        <v>0.18</v>
+      </c>
+      <c r="H52">
+        <v>1.32</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.2</v>
+      </c>
+      <c r="K52">
+        <v>0.263</v>
+      </c>
+      <c r="L52">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M52">
+        <v>0.029502</v>
+      </c>
+      <c r="N52">
+        <v>0.9074979999999999</v>
+      </c>
+      <c r="O52">
+        <v>0.11343725</v>
+      </c>
+      <c r="P52">
+        <v>0.7940607499999999</v>
+      </c>
+      <c r="Q52">
+        <v>1.05706075</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1213863934876931</v>
+      </c>
+      <c r="T52">
+        <v>1.507972706701945</v>
+      </c>
+      <c r="U52">
+        <v>0.0447</v>
+      </c>
+      <c r="V52">
+        <v>0.125</v>
+      </c>
+      <c r="W52">
+        <v>0.0391125</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>31.76055860619618</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08019751414818811</v>
+      </c>
+      <c r="C53">
+        <v>0.664516422183395</v>
+      </c>
+      <c r="D53">
+        <v>1.157716422183395</v>
+      </c>
+      <c r="E53">
+        <v>0.6732</v>
+      </c>
+      <c r="F53">
+        <v>0.6732</v>
+      </c>
+      <c r="G53">
+        <v>0.18</v>
+      </c>
+      <c r="H53">
+        <v>1.32</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.2</v>
+      </c>
+      <c r="K53">
+        <v>0.263</v>
+      </c>
+      <c r="L53">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M53">
+        <v>0.03009204</v>
+      </c>
+      <c r="N53">
+        <v>0.90690796</v>
+      </c>
+      <c r="O53">
+        <v>0.113363495</v>
+      </c>
+      <c r="P53">
+        <v>0.793544465</v>
+      </c>
+      <c r="Q53">
+        <v>1.056544465</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1229594676493635</v>
+      </c>
+      <c r="T53">
+        <v>1.536695996353411</v>
+      </c>
+      <c r="U53">
+        <v>0.0447</v>
+      </c>
+      <c r="V53">
+        <v>0.125</v>
+      </c>
+      <c r="W53">
+        <v>0.0391125</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>31.1378025550943</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08014558155252965</v>
+      </c>
+      <c r="C54">
+        <v>0.6516693090908164</v>
+      </c>
+      <c r="D54">
+        <v>1.158069309090817</v>
+      </c>
+      <c r="E54">
+        <v>0.6864</v>
+      </c>
+      <c r="F54">
+        <v>0.6864</v>
+      </c>
+      <c r="G54">
+        <v>0.18</v>
+      </c>
+      <c r="H54">
+        <v>1.32</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.2</v>
+      </c>
+      <c r="K54">
+        <v>0.263</v>
+      </c>
+      <c r="L54">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M54">
+        <v>0.03068208</v>
+      </c>
+      <c r="N54">
+        <v>0.9063179199999999</v>
+      </c>
+      <c r="O54">
+        <v>0.11328974</v>
+      </c>
+      <c r="P54">
+        <v>0.7930281799999999</v>
+      </c>
+      <c r="Q54">
+        <v>1.05602818</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1245980865677701</v>
+      </c>
+      <c r="T54">
+        <v>1.566616089740354</v>
+      </c>
+      <c r="U54">
+        <v>0.0447</v>
+      </c>
+      <c r="V54">
+        <v>0.125</v>
+      </c>
+      <c r="W54">
+        <v>0.0391125</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>30.53899865980402</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08009364895687118</v>
+      </c>
+      <c r="C55">
+        <v>0.6388224111927995</v>
+      </c>
+      <c r="D55">
+        <v>1.1584224111928</v>
+      </c>
+      <c r="E55">
+        <v>0.6996000000000001</v>
+      </c>
+      <c r="F55">
+        <v>0.6996000000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.18</v>
+      </c>
+      <c r="H55">
+        <v>1.32</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.2</v>
+      </c>
+      <c r="K55">
+        <v>0.263</v>
+      </c>
+      <c r="L55">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M55">
+        <v>0.03127212000000001</v>
+      </c>
+      <c r="N55">
+        <v>0.9057278799999999</v>
+      </c>
+      <c r="O55">
+        <v>0.113215985</v>
+      </c>
+      <c r="P55">
+        <v>0.792511895</v>
+      </c>
+      <c r="Q55">
+        <v>1.055511895</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1263064339507898</v>
+      </c>
+      <c r="T55">
+        <v>1.597809378590572</v>
+      </c>
+      <c r="U55">
+        <v>0.0447</v>
+      </c>
+      <c r="V55">
+        <v>0.125</v>
+      </c>
+      <c r="W55">
+        <v>0.0391125</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>29.96279113792092</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08004171636121273</v>
+      </c>
+      <c r="C56">
+        <v>0.6259757286862471</v>
+      </c>
+      <c r="D56">
+        <v>1.158775728686247</v>
+      </c>
+      <c r="E56">
+        <v>0.7128000000000001</v>
+      </c>
+      <c r="F56">
+        <v>0.7128000000000001</v>
+      </c>
+      <c r="G56">
+        <v>0.18</v>
+      </c>
+      <c r="H56">
+        <v>1.32</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.2</v>
+      </c>
+      <c r="K56">
+        <v>0.263</v>
+      </c>
+      <c r="L56">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M56">
+        <v>0.03186216000000001</v>
+      </c>
+      <c r="N56">
+        <v>0.90513784</v>
+      </c>
+      <c r="O56">
+        <v>0.11314223</v>
+      </c>
+      <c r="P56">
+        <v>0.79199561</v>
+      </c>
+      <c r="Q56">
+        <v>1.05499561</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1280890573069842</v>
+      </c>
+      <c r="T56">
+        <v>1.630358897390799</v>
+      </c>
+      <c r="U56">
+        <v>0.0447</v>
+      </c>
+      <c r="V56">
+        <v>0.125</v>
+      </c>
+      <c r="W56">
+        <v>0.0391125</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>29.40792463536684</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.07998978376555425</v>
+      </c>
+      <c r="C57">
+        <v>0.6131292617683014</v>
+      </c>
+      <c r="D57">
+        <v>1.159129261768302</v>
+      </c>
+      <c r="E57">
+        <v>0.7260000000000001</v>
+      </c>
+      <c r="F57">
+        <v>0.7260000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.18</v>
+      </c>
+      <c r="H57">
+        <v>1.32</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.2</v>
+      </c>
+      <c r="K57">
+        <v>0.263</v>
+      </c>
+      <c r="L57">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M57">
+        <v>0.03245220000000001</v>
+      </c>
+      <c r="N57">
+        <v>0.9045477999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.113068475</v>
+      </c>
+      <c r="P57">
+        <v>0.791479325</v>
+      </c>
+      <c r="Q57">
+        <v>1.054479325</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1299509083678984</v>
+      </c>
+      <c r="T57">
+        <v>1.664355061471036</v>
+      </c>
+      <c r="U57">
+        <v>0.0447</v>
+      </c>
+      <c r="V57">
+        <v>0.125</v>
+      </c>
+      <c r="W57">
+        <v>0.0391125</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>28.87323509654198</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.0799378511698958</v>
+      </c>
+      <c r="C58">
+        <v>0.6002830106363453</v>
+      </c>
+      <c r="D58">
+        <v>1.159483010636345</v>
+      </c>
+      <c r="E58">
+        <v>0.7392000000000001</v>
+      </c>
+      <c r="F58">
+        <v>0.7392000000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.18</v>
+      </c>
+      <c r="H58">
+        <v>1.32</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.2</v>
+      </c>
+      <c r="K58">
+        <v>0.263</v>
+      </c>
+      <c r="L58">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M58">
+        <v>0.03304224000000001</v>
+      </c>
+      <c r="N58">
+        <v>0.9039577599999999</v>
+      </c>
+      <c r="O58">
+        <v>0.11299472</v>
+      </c>
+      <c r="P58">
+        <v>0.79096304</v>
+      </c>
+      <c r="Q58">
+        <v>1.05396304</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1318973890224905</v>
+      </c>
+      <c r="T58">
+        <v>1.699896505736738</v>
+      </c>
+      <c r="U58">
+        <v>0.0447</v>
+      </c>
+      <c r="V58">
+        <v>0.125</v>
+      </c>
+      <c r="W58">
+        <v>0.0391125</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>28.35764161267516</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.07988591857423732</v>
+      </c>
+      <c r="C59">
+        <v>0.5874369754880037</v>
+      </c>
+      <c r="D59">
+        <v>1.159836975488004</v>
+      </c>
+      <c r="E59">
+        <v>0.7524000000000001</v>
+      </c>
+      <c r="F59">
+        <v>0.7524000000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.18</v>
+      </c>
+      <c r="H59">
+        <v>1.32</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.2</v>
+      </c>
+      <c r="K59">
+        <v>0.263</v>
+      </c>
+      <c r="L59">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M59">
+        <v>0.03363228000000001</v>
+      </c>
+      <c r="N59">
+        <v>0.90336772</v>
+      </c>
+      <c r="O59">
+        <v>0.112920965</v>
+      </c>
+      <c r="P59">
+        <v>0.7904467549999999</v>
+      </c>
+      <c r="Q59">
+        <v>1.053446755</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1339344036610171</v>
+      </c>
+      <c r="T59">
+        <v>1.737091040433403</v>
+      </c>
+      <c r="U59">
+        <v>0.0447</v>
+      </c>
+      <c r="V59">
+        <v>0.125</v>
+      </c>
+      <c r="W59">
+        <v>0.0391125</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>27.86013912824227</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.07983398597857888</v>
+      </c>
+      <c r="C60">
+        <v>0.5745911565211416</v>
+      </c>
+      <c r="D60">
+        <v>1.160191156521142</v>
+      </c>
+      <c r="E60">
+        <v>0.7655999999999999</v>
+      </c>
+      <c r="F60">
+        <v>0.7655999999999999</v>
+      </c>
+      <c r="G60">
+        <v>0.18</v>
+      </c>
+      <c r="H60">
+        <v>1.32</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.2</v>
+      </c>
+      <c r="K60">
+        <v>0.263</v>
+      </c>
+      <c r="L60">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M60">
+        <v>0.03422232</v>
+      </c>
+      <c r="N60">
+        <v>0.9027776799999999</v>
+      </c>
+      <c r="O60">
+        <v>0.11284721</v>
+      </c>
+      <c r="P60">
+        <v>0.7899304699999999</v>
+      </c>
+      <c r="Q60">
+        <v>1.05293047</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1360684189966164</v>
+      </c>
+      <c r="T60">
+        <v>1.776056743448957</v>
+      </c>
+      <c r="U60">
+        <v>0.0447</v>
+      </c>
+      <c r="V60">
+        <v>0.125</v>
+      </c>
+      <c r="W60">
+        <v>0.0391125</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>27.37979190189326</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.07978205338292041</v>
+      </c>
+      <c r="C61">
+        <v>0.5617455539338668</v>
+      </c>
+      <c r="D61">
+        <v>1.160545553933867</v>
+      </c>
+      <c r="E61">
+        <v>0.7788</v>
+      </c>
+      <c r="F61">
+        <v>0.7788</v>
+      </c>
+      <c r="G61">
+        <v>0.18</v>
+      </c>
+      <c r="H61">
+        <v>1.32</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.2</v>
+      </c>
+      <c r="K61">
+        <v>0.263</v>
+      </c>
+      <c r="L61">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M61">
+        <v>0.03481236000000001</v>
+      </c>
+      <c r="N61">
+        <v>0.90218764</v>
+      </c>
+      <c r="O61">
+        <v>0.112773455</v>
+      </c>
+      <c r="P61">
+        <v>0.7894141849999999</v>
+      </c>
+      <c r="Q61">
+        <v>1.052414185</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1383065326412693</v>
+      </c>
+      <c r="T61">
+        <v>1.81692321246527</v>
+      </c>
+      <c r="U61">
+        <v>0.0447</v>
+      </c>
+      <c r="V61">
+        <v>0.125</v>
+      </c>
+      <c r="W61">
+        <v>0.0391125</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>26.91572763236965</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.07973012078726195</v>
+      </c>
+      <c r="C62">
+        <v>0.5489001679245287</v>
+      </c>
+      <c r="D62">
+        <v>1.160900167924529</v>
+      </c>
+      <c r="E62">
+        <v>0.792</v>
+      </c>
+      <c r="F62">
+        <v>0.792</v>
+      </c>
+      <c r="G62">
+        <v>0.18</v>
+      </c>
+      <c r="H62">
+        <v>1.32</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.2</v>
+      </c>
+      <c r="K62">
+        <v>0.263</v>
+      </c>
+      <c r="L62">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M62">
+        <v>0.03540240000000001</v>
+      </c>
+      <c r="N62">
+        <v>0.9015975999999999</v>
+      </c>
+      <c r="O62">
+        <v>0.1126997</v>
+      </c>
+      <c r="P62">
+        <v>0.7888978999999999</v>
+      </c>
+      <c r="Q62">
+        <v>1.0518979</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1406565519681549</v>
+      </c>
+      <c r="T62">
+        <v>1.859833004932399</v>
+      </c>
+      <c r="U62">
+        <v>0.0447</v>
+      </c>
+      <c r="V62">
+        <v>0.125</v>
+      </c>
+      <c r="W62">
+        <v>0.0391125</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>26.46713217183015</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.07967818819160349</v>
+      </c>
+      <c r="C63">
+        <v>0.5360549986917197</v>
+      </c>
+      <c r="D63">
+        <v>1.16125499869172</v>
+      </c>
+      <c r="E63">
+        <v>0.8052</v>
+      </c>
+      <c r="F63">
+        <v>0.8052</v>
+      </c>
+      <c r="G63">
+        <v>0.18</v>
+      </c>
+      <c r="H63">
+        <v>1.32</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.2</v>
+      </c>
+      <c r="K63">
+        <v>0.263</v>
+      </c>
+      <c r="L63">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M63">
+        <v>0.03599244000000001</v>
+      </c>
+      <c r="N63">
+        <v>0.9010075599999999</v>
+      </c>
+      <c r="O63">
+        <v>0.112625945</v>
+      </c>
+      <c r="P63">
+        <v>0.7883816149999999</v>
+      </c>
+      <c r="Q63">
+        <v>1.051381615</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1431270851066756</v>
+      </c>
+      <c r="T63">
+        <v>1.904943299577329</v>
+      </c>
+      <c r="U63">
+        <v>0.0447</v>
+      </c>
+      <c r="V63">
+        <v>0.125</v>
+      </c>
+      <c r="W63">
+        <v>0.0391125</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>26.0332447591772</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.07962625559594502</v>
+      </c>
+      <c r="C64">
+        <v>0.5232100464342744</v>
+      </c>
+      <c r="D64">
+        <v>1.161610046434274</v>
+      </c>
+      <c r="E64">
+        <v>0.8184</v>
+      </c>
+      <c r="F64">
+        <v>0.8184</v>
+      </c>
+      <c r="G64">
+        <v>0.18</v>
+      </c>
+      <c r="H64">
+        <v>1.32</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.2</v>
+      </c>
+      <c r="K64">
+        <v>0.263</v>
+      </c>
+      <c r="L64">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M64">
+        <v>0.03658248</v>
+      </c>
+      <c r="N64">
+        <v>0.90041752</v>
+      </c>
+      <c r="O64">
+        <v>0.11255219</v>
+      </c>
+      <c r="P64">
+        <v>0.78786533</v>
+      </c>
+      <c r="Q64">
+        <v>1.05086533</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1457276463051185</v>
+      </c>
+      <c r="T64">
+        <v>1.952427820256202</v>
+      </c>
+      <c r="U64">
+        <v>0.0447</v>
+      </c>
+      <c r="V64">
+        <v>0.125</v>
+      </c>
+      <c r="W64">
+        <v>0.0391125</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>25.61335371467435</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.07957432300028656</v>
+      </c>
+      <c r="C65">
+        <v>0.5103653113512711</v>
+      </c>
+      <c r="D65">
+        <v>1.161965311351271</v>
+      </c>
+      <c r="E65">
+        <v>0.8316</v>
+      </c>
+      <c r="F65">
+        <v>0.8316</v>
+      </c>
+      <c r="G65">
+        <v>0.18</v>
+      </c>
+      <c r="H65">
+        <v>1.32</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.2</v>
+      </c>
+      <c r="K65">
+        <v>0.263</v>
+      </c>
+      <c r="L65">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M65">
+        <v>0.03717252</v>
+      </c>
+      <c r="N65">
+        <v>0.8998274799999999</v>
+      </c>
+      <c r="O65">
+        <v>0.112478435</v>
+      </c>
+      <c r="P65">
+        <v>0.7873490449999999</v>
+      </c>
+      <c r="Q65">
+        <v>1.050349045</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1484687783791529</v>
+      </c>
+      <c r="T65">
+        <v>2.002479071782583</v>
+      </c>
+      <c r="U65">
+        <v>0.0447</v>
+      </c>
+      <c r="V65">
+        <v>0.125</v>
+      </c>
+      <c r="W65">
+        <v>0.0391125</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>25.20679254460015</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.07952239040462809</v>
+      </c>
+      <c r="C66">
+        <v>0.4975207936420313</v>
+      </c>
+      <c r="D66">
+        <v>1.162320793642031</v>
+      </c>
+      <c r="E66">
+        <v>0.8448000000000001</v>
+      </c>
+      <c r="F66">
+        <v>0.8448000000000001</v>
+      </c>
+      <c r="G66">
+        <v>0.18</v>
+      </c>
+      <c r="H66">
+        <v>1.32</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.2</v>
+      </c>
+      <c r="K66">
+        <v>0.263</v>
+      </c>
+      <c r="L66">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M66">
+        <v>0.03776256000000001</v>
+      </c>
+      <c r="N66">
+        <v>0.8992374399999999</v>
+      </c>
+      <c r="O66">
+        <v>0.11240468</v>
+      </c>
+      <c r="P66">
+        <v>0.7868327599999999</v>
+      </c>
+      <c r="Q66">
+        <v>1.04983276</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1513621955684114</v>
+      </c>
+      <c r="T66">
+        <v>2.055310948393762</v>
+      </c>
+      <c r="U66">
+        <v>0.0447</v>
+      </c>
+      <c r="V66">
+        <v>0.125</v>
+      </c>
+      <c r="W66">
+        <v>0.0391125</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>24.81293641109077</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.07947045780896965</v>
+      </c>
+      <c r="C67">
+        <v>0.484676493506121</v>
+      </c>
+      <c r="D67">
+        <v>1.162676493506121</v>
+      </c>
+      <c r="E67">
+        <v>0.8580000000000001</v>
+      </c>
+      <c r="F67">
+        <v>0.8580000000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.18</v>
+      </c>
+      <c r="H67">
+        <v>1.32</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.2</v>
+      </c>
+      <c r="K67">
+        <v>0.263</v>
+      </c>
+      <c r="L67">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M67">
+        <v>0.03835260000000001</v>
+      </c>
+      <c r="N67">
+        <v>0.8986474</v>
+      </c>
+      <c r="O67">
+        <v>0.112330925</v>
+      </c>
+      <c r="P67">
+        <v>0.786316475</v>
+      </c>
+      <c r="Q67">
+        <v>1.049316475</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1544209508827704</v>
+      </c>
+      <c r="T67">
+        <v>2.111161789382723</v>
+      </c>
+      <c r="U67">
+        <v>0.0447</v>
+      </c>
+      <c r="V67">
+        <v>0.125</v>
+      </c>
+      <c r="W67">
+        <v>0.0391125</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>24.43119892784322</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.07941852521331116</v>
+      </c>
+      <c r="C68">
+        <v>0.4718324111433504</v>
+      </c>
+      <c r="D68">
+        <v>1.163032411143351</v>
+      </c>
+      <c r="E68">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="F68">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.18</v>
+      </c>
+      <c r="H68">
+        <v>1.32</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.2</v>
+      </c>
+      <c r="K68">
+        <v>0.263</v>
+      </c>
+      <c r="L68">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M68">
+        <v>0.03894264000000001</v>
+      </c>
+      <c r="N68">
+        <v>0.8980573599999999</v>
+      </c>
+      <c r="O68">
+        <v>0.11225717</v>
+      </c>
+      <c r="P68">
+        <v>0.7858001899999999</v>
+      </c>
+      <c r="Q68">
+        <v>1.04880019</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.157659632980327</v>
+      </c>
+      <c r="T68">
+        <v>2.17029797395927</v>
+      </c>
+      <c r="U68">
+        <v>0.0447</v>
+      </c>
+      <c r="V68">
+        <v>0.125</v>
+      </c>
+      <c r="W68">
+        <v>0.0391125</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>24.06102924711832</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.07936659261765272</v>
+      </c>
+      <c r="C69">
+        <v>0.4589885467537744</v>
+      </c>
+      <c r="D69">
+        <v>1.163388546753775</v>
+      </c>
+      <c r="E69">
+        <v>0.8844000000000001</v>
+      </c>
+      <c r="F69">
+        <v>0.8844000000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.18</v>
+      </c>
+      <c r="H69">
+        <v>1.32</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.2</v>
+      </c>
+      <c r="K69">
+        <v>0.263</v>
+      </c>
+      <c r="L69">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M69">
+        <v>0.03953268000000001</v>
+      </c>
+      <c r="N69">
+        <v>0.89746732</v>
+      </c>
+      <c r="O69">
+        <v>0.112183415</v>
+      </c>
+      <c r="P69">
+        <v>0.785283905</v>
+      </c>
+      <c r="Q69">
+        <v>1.048283905</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1610945988413719</v>
+      </c>
+      <c r="T69">
+        <v>2.233018169722274</v>
+      </c>
+      <c r="U69">
+        <v>0.0447</v>
+      </c>
+      <c r="V69">
+        <v>0.125</v>
+      </c>
+      <c r="W69">
+        <v>0.0391125</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>23.70190940760909</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.07931466002199425</v>
+      </c>
+      <c r="C70">
+        <v>0.4461449005376928</v>
+      </c>
+      <c r="D70">
+        <v>1.163744900537693</v>
+      </c>
+      <c r="E70">
+        <v>0.8976000000000001</v>
+      </c>
+      <c r="F70">
+        <v>0.8976000000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.18</v>
+      </c>
+      <c r="H70">
+        <v>1.32</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.2</v>
+      </c>
+      <c r="K70">
+        <v>0.263</v>
+      </c>
+      <c r="L70">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M70">
+        <v>0.04012272000000001</v>
+      </c>
+      <c r="N70">
+        <v>0.8968772799999999</v>
+      </c>
+      <c r="O70">
+        <v>0.11210966</v>
+      </c>
+      <c r="P70">
+        <v>0.7847676199999999</v>
+      </c>
+      <c r="Q70">
+        <v>1.04776762</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1647442500687321</v>
+      </c>
+      <c r="T70">
+        <v>2.299658377720466</v>
+      </c>
+      <c r="U70">
+        <v>0.0447</v>
+      </c>
+      <c r="V70">
+        <v>0.125</v>
+      </c>
+      <c r="W70">
+        <v>0.0391125</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>23.35335191632072</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.07926272742633579</v>
+      </c>
+      <c r="C71">
+        <v>0.4333014726956511</v>
+      </c>
+      <c r="D71">
+        <v>1.164101472695651</v>
+      </c>
+      <c r="E71">
+        <v>0.9108000000000002</v>
+      </c>
+      <c r="F71">
+        <v>0.9108000000000002</v>
+      </c>
+      <c r="G71">
+        <v>0.18</v>
+      </c>
+      <c r="H71">
+        <v>1.32</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.2</v>
+      </c>
+      <c r="K71">
+        <v>0.263</v>
+      </c>
+      <c r="L71">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M71">
+        <v>0.04071276000000001</v>
+      </c>
+      <c r="N71">
+        <v>0.8962872399999999</v>
+      </c>
+      <c r="O71">
+        <v>0.112035905</v>
+      </c>
+      <c r="P71">
+        <v>0.784251335</v>
+      </c>
+      <c r="Q71">
+        <v>1.047251335</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1686293626655994</v>
+      </c>
+      <c r="T71">
+        <v>2.370597953976606</v>
+      </c>
+      <c r="U71">
+        <v>0.0447</v>
+      </c>
+      <c r="V71">
+        <v>0.125</v>
+      </c>
+      <c r="W71">
+        <v>0.0391125</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>23.01489754072187</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.07921079483067732</v>
+      </c>
+      <c r="C72">
+        <v>0.4204582634284411</v>
+      </c>
+      <c r="D72">
+        <v>1.164458263428441</v>
+      </c>
+      <c r="E72">
+        <v>0.9240000000000002</v>
+      </c>
+      <c r="F72">
+        <v>0.9240000000000002</v>
+      </c>
+      <c r="G72">
+        <v>0.18</v>
+      </c>
+      <c r="H72">
+        <v>1.32</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.2</v>
+      </c>
+      <c r="K72">
+        <v>0.263</v>
+      </c>
+      <c r="L72">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M72">
+        <v>0.04130280000000001</v>
+      </c>
+      <c r="N72">
+        <v>0.8956972</v>
+      </c>
+      <c r="O72">
+        <v>0.11196215</v>
+      </c>
+      <c r="P72">
+        <v>0.78373505</v>
+      </c>
+      <c r="Q72">
+        <v>1.04673505</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1727734827689244</v>
+      </c>
+      <c r="T72">
+        <v>2.446266835316488</v>
+      </c>
+      <c r="U72">
+        <v>0.0447</v>
+      </c>
+      <c r="V72">
+        <v>0.125</v>
+      </c>
+      <c r="W72">
+        <v>0.0391125</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>22.68611329014013</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.07915886223501888</v>
+      </c>
+      <c r="C73">
+        <v>0.4076152729370999</v>
+      </c>
+      <c r="D73">
+        <v>1.1648152729371</v>
+      </c>
+      <c r="E73">
+        <v>0.9372</v>
+      </c>
+      <c r="F73">
+        <v>0.9372</v>
+      </c>
+      <c r="G73">
+        <v>0.18</v>
+      </c>
+      <c r="H73">
+        <v>1.32</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.2</v>
+      </c>
+      <c r="K73">
+        <v>0.263</v>
+      </c>
+      <c r="L73">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M73">
+        <v>0.04189284000000001</v>
+      </c>
+      <c r="N73">
+        <v>0.8951071599999999</v>
+      </c>
+      <c r="O73">
+        <v>0.111888395</v>
+      </c>
+      <c r="P73">
+        <v>0.7832187649999999</v>
+      </c>
+      <c r="Q73">
+        <v>1.046218765</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1772034042586857</v>
+      </c>
+      <c r="T73">
+        <v>2.527154260197052</v>
+      </c>
+      <c r="U73">
+        <v>0.0447</v>
+      </c>
+      <c r="V73">
+        <v>0.125</v>
+      </c>
+      <c r="W73">
+        <v>0.0391125</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>22.36659056774379</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.07910692963936042</v>
+      </c>
+      <c r="C74">
+        <v>0.3947725014229116</v>
+      </c>
+      <c r="D74">
+        <v>1.165172501422912</v>
+      </c>
+      <c r="E74">
+        <v>0.9504</v>
+      </c>
+      <c r="F74">
+        <v>0.9504</v>
+      </c>
+      <c r="G74">
+        <v>0.18</v>
+      </c>
+      <c r="H74">
+        <v>1.32</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.2</v>
+      </c>
+      <c r="K74">
+        <v>0.263</v>
+      </c>
+      <c r="L74">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M74">
+        <v>0.04248288000000001</v>
+      </c>
+      <c r="N74">
+        <v>0.8945171199999999</v>
+      </c>
+      <c r="O74">
+        <v>0.11181464</v>
+      </c>
+      <c r="P74">
+        <v>0.78270248</v>
+      </c>
+      <c r="Q74">
+        <v>1.04570248</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1819497487120015</v>
+      </c>
+      <c r="T74">
+        <v>2.613819358283371</v>
+      </c>
+      <c r="U74">
+        <v>0.0447</v>
+      </c>
+      <c r="V74">
+        <v>0.125</v>
+      </c>
+      <c r="W74">
+        <v>0.0391125</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>22.05594347652513</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.07905499704370195</v>
+      </c>
+      <c r="C75">
+        <v>0.381929949087408</v>
+      </c>
+      <c r="D75">
+        <v>1.165529949087408</v>
+      </c>
+      <c r="E75">
+        <v>0.9636</v>
+      </c>
+      <c r="F75">
+        <v>0.9636</v>
+      </c>
+      <c r="G75">
+        <v>0.18</v>
+      </c>
+      <c r="H75">
+        <v>1.32</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.2</v>
+      </c>
+      <c r="K75">
+        <v>0.263</v>
+      </c>
+      <c r="L75">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M75">
+        <v>0.04307292</v>
+      </c>
+      <c r="N75">
+        <v>0.89392708</v>
+      </c>
+      <c r="O75">
+        <v>0.111740885</v>
+      </c>
+      <c r="P75">
+        <v>0.782186195</v>
+      </c>
+      <c r="Q75">
+        <v>1.045186195</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1870476742359331</v>
+      </c>
+      <c r="T75">
+        <v>2.706904093264972</v>
+      </c>
+      <c r="U75">
+        <v>0.0447</v>
+      </c>
+      <c r="V75">
+        <v>0.125</v>
+      </c>
+      <c r="W75">
+        <v>0.0391125</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>21.75380726451794</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.07900306444804348</v>
+      </c>
+      <c r="C76">
+        <v>0.369087616132367</v>
+      </c>
+      <c r="D76">
+        <v>1.165887616132367</v>
+      </c>
+      <c r="E76">
+        <v>0.9768</v>
+      </c>
+      <c r="F76">
+        <v>0.9768</v>
+      </c>
+      <c r="G76">
+        <v>0.18</v>
+      </c>
+      <c r="H76">
+        <v>1.32</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.2</v>
+      </c>
+      <c r="K76">
+        <v>0.263</v>
+      </c>
+      <c r="L76">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M76">
+        <v>0.04366296</v>
+      </c>
+      <c r="N76">
+        <v>0.8933370399999999</v>
+      </c>
+      <c r="O76">
+        <v>0.11166713</v>
+      </c>
+      <c r="P76">
+        <v>0.78166991</v>
+      </c>
+      <c r="Q76">
+        <v>1.04466991</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1925377478770903</v>
+      </c>
+      <c r="T76">
+        <v>2.807149192475928</v>
+      </c>
+      <c r="U76">
+        <v>0.0447</v>
+      </c>
+      <c r="V76">
+        <v>0.125</v>
+      </c>
+      <c r="W76">
+        <v>0.0391125</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>21.4598368960785</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.07895113185238502</v>
+      </c>
+      <c r="C77">
+        <v>0.3562455027598155</v>
+      </c>
+      <c r="D77">
+        <v>1.166245502759816</v>
+      </c>
+      <c r="E77">
+        <v>0.99</v>
+      </c>
+      <c r="F77">
+        <v>0.99</v>
+      </c>
+      <c r="G77">
+        <v>0.18</v>
+      </c>
+      <c r="H77">
+        <v>1.32</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.2</v>
+      </c>
+      <c r="K77">
+        <v>0.263</v>
+      </c>
+      <c r="L77">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M77">
+        <v>0.044253</v>
+      </c>
+      <c r="N77">
+        <v>0.892747</v>
+      </c>
+      <c r="O77">
+        <v>0.111593375</v>
+      </c>
+      <c r="P77">
+        <v>0.781153625</v>
+      </c>
+      <c r="Q77">
+        <v>1.044153625</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1984670274095401</v>
+      </c>
+      <c r="T77">
+        <v>2.91541389962376</v>
+      </c>
+      <c r="U77">
+        <v>0.0447</v>
+      </c>
+      <c r="V77">
+        <v>0.125</v>
+      </c>
+      <c r="W77">
+        <v>0.0391125</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>21.17370573746413</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.07889919925672656</v>
+      </c>
+      <c r="C78">
+        <v>0.3434036091720276</v>
+      </c>
+      <c r="D78">
+        <v>1.166603609172028</v>
+      </c>
+      <c r="E78">
+        <v>1.0032</v>
+      </c>
+      <c r="F78">
+        <v>1.0032</v>
+      </c>
+      <c r="G78">
+        <v>0.18</v>
+      </c>
+      <c r="H78">
+        <v>1.32</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.2</v>
+      </c>
+      <c r="K78">
+        <v>0.263</v>
+      </c>
+      <c r="L78">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M78">
+        <v>0.04484304000000001</v>
+      </c>
+      <c r="N78">
+        <v>0.8921569599999999</v>
+      </c>
+      <c r="O78">
+        <v>0.11151962</v>
+      </c>
+      <c r="P78">
+        <v>0.78063734</v>
+      </c>
+      <c r="Q78">
+        <v>1.04363734</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.204890413569694</v>
+      </c>
+      <c r="T78">
+        <v>3.032700665700578</v>
+      </c>
+      <c r="U78">
+        <v>0.0447</v>
+      </c>
+      <c r="V78">
+        <v>0.125</v>
+      </c>
+      <c r="W78">
+        <v>0.0391125</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>20.8951043461817</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.07884726666106809</v>
+      </c>
+      <c r="C79">
+        <v>0.3305619355715266</v>
+      </c>
+      <c r="D79">
+        <v>1.166961935571527</v>
+      </c>
+      <c r="E79">
+        <v>1.0164</v>
+      </c>
+      <c r="F79">
+        <v>1.0164</v>
+      </c>
+      <c r="G79">
+        <v>0.18</v>
+      </c>
+      <c r="H79">
+        <v>1.32</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.2</v>
+      </c>
+      <c r="K79">
+        <v>0.263</v>
+      </c>
+      <c r="L79">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M79">
+        <v>0.04543308</v>
+      </c>
+      <c r="N79">
+        <v>0.8915669199999999</v>
+      </c>
+      <c r="O79">
+        <v>0.111445865</v>
+      </c>
+      <c r="P79">
+        <v>0.780121055</v>
+      </c>
+      <c r="Q79">
+        <v>1.043121055</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2118723550481221</v>
+      </c>
+      <c r="T79">
+        <v>3.160186281001467</v>
+      </c>
+      <c r="U79">
+        <v>0.0447</v>
+      </c>
+      <c r="V79">
+        <v>0.125</v>
+      </c>
+      <c r="W79">
+        <v>0.0391125</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>20.62373935467285</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.07879533406540963</v>
+      </c>
+      <c r="C80">
+        <v>0.3177204821610837</v>
+      </c>
+      <c r="D80">
+        <v>1.167320482161084</v>
+      </c>
+      <c r="E80">
+        <v>1.0296</v>
+      </c>
+      <c r="F80">
+        <v>1.0296</v>
+      </c>
+      <c r="G80">
+        <v>0.18</v>
+      </c>
+      <c r="H80">
+        <v>1.32</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.2</v>
+      </c>
+      <c r="K80">
+        <v>0.263</v>
+      </c>
+      <c r="L80">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M80">
+        <v>0.04602312000000001</v>
+      </c>
+      <c r="N80">
+        <v>0.89097688</v>
+      </c>
+      <c r="O80">
+        <v>0.11137211</v>
+      </c>
+      <c r="P80">
+        <v>0.7796047699999999</v>
+      </c>
+      <c r="Q80">
+        <v>1.04260477</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2194890184791347</v>
+      </c>
+      <c r="T80">
+        <v>3.299261497693346</v>
+      </c>
+      <c r="U80">
+        <v>0.0447</v>
+      </c>
+      <c r="V80">
+        <v>0.125</v>
+      </c>
+      <c r="W80">
+        <v>0.0391125</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>20.35933243986935</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.07874340146975117</v>
+      </c>
+      <c r="C81">
+        <v>0.3048792491437207</v>
+      </c>
+      <c r="D81">
+        <v>1.167679249143721</v>
+      </c>
+      <c r="E81">
+        <v>1.0428</v>
+      </c>
+      <c r="F81">
+        <v>1.0428</v>
+      </c>
+      <c r="G81">
+        <v>0.18</v>
+      </c>
+      <c r="H81">
+        <v>1.32</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.2</v>
+      </c>
+      <c r="K81">
+        <v>0.263</v>
+      </c>
+      <c r="L81">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M81">
+        <v>0.04661316000000001</v>
+      </c>
+      <c r="N81">
+        <v>0.8903868399999999</v>
+      </c>
+      <c r="O81">
+        <v>0.111298355</v>
+      </c>
+      <c r="P81">
+        <v>0.7790884849999999</v>
+      </c>
+      <c r="Q81">
+        <v>1.042088485</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2278310784273866</v>
+      </c>
+      <c r="T81">
+        <v>3.451581973117786</v>
+      </c>
+      <c r="U81">
+        <v>0.0447</v>
+      </c>
+      <c r="V81">
+        <v>0.125</v>
+      </c>
+      <c r="W81">
+        <v>0.0391125</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>20.10161937101024</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.0786914688740927</v>
+      </c>
+      <c r="C82">
+        <v>0.2920382367227088</v>
+      </c>
+      <c r="D82">
+        <v>1.168038236722709</v>
+      </c>
+      <c r="E82">
+        <v>1.056</v>
+      </c>
+      <c r="F82">
+        <v>1.056</v>
+      </c>
+      <c r="G82">
+        <v>0.18</v>
+      </c>
+      <c r="H82">
+        <v>1.32</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.2</v>
+      </c>
+      <c r="K82">
+        <v>0.263</v>
+      </c>
+      <c r="L82">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M82">
+        <v>0.04720320000000001</v>
+      </c>
+      <c r="N82">
+        <v>0.8897967999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.1112246</v>
+      </c>
+      <c r="P82">
+        <v>0.7785721999999999</v>
+      </c>
+      <c r="Q82">
+        <v>1.0415722</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2370073443704636</v>
+      </c>
+      <c r="T82">
+        <v>3.619134496084668</v>
+      </c>
+      <c r="U82">
+        <v>0.0447</v>
+      </c>
+      <c r="V82">
+        <v>0.125</v>
+      </c>
+      <c r="W82">
+        <v>0.0391125</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>19.85034912887262</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.07863953627843426</v>
+      </c>
+      <c r="C83">
+        <v>0.2791974451015677</v>
+      </c>
+      <c r="D83">
+        <v>1.168397445101568</v>
+      </c>
+      <c r="E83">
+        <v>1.0692</v>
+      </c>
+      <c r="F83">
+        <v>1.0692</v>
+      </c>
+      <c r="G83">
+        <v>0.18</v>
+      </c>
+      <c r="H83">
+        <v>1.32</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.2</v>
+      </c>
+      <c r="K83">
+        <v>0.263</v>
+      </c>
+      <c r="L83">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M83">
+        <v>0.04779324000000001</v>
+      </c>
+      <c r="N83">
+        <v>0.88920676</v>
+      </c>
+      <c r="O83">
+        <v>0.111150845</v>
+      </c>
+      <c r="P83">
+        <v>0.7780559149999999</v>
+      </c>
+      <c r="Q83">
+        <v>1.041055915</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2471495330443908</v>
+      </c>
+      <c r="T83">
+        <v>3.804324126732276</v>
+      </c>
+      <c r="U83">
+        <v>0.0447</v>
+      </c>
+      <c r="V83">
+        <v>0.125</v>
+      </c>
+      <c r="W83">
+        <v>0.0391125</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>19.60528309024456</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.07858760368277579</v>
+      </c>
+      <c r="C84">
+        <v>0.2663568744840701</v>
+      </c>
+      <c r="D84">
+        <v>1.16875687448407</v>
+      </c>
+      <c r="E84">
+        <v>1.0824</v>
+      </c>
+      <c r="F84">
+        <v>1.0824</v>
+      </c>
+      <c r="G84">
+        <v>0.18</v>
+      </c>
+      <c r="H84">
+        <v>1.32</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.2</v>
+      </c>
+      <c r="K84">
+        <v>0.263</v>
+      </c>
+      <c r="L84">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M84">
+        <v>0.04838328000000001</v>
+      </c>
+      <c r="N84">
+        <v>0.8886167199999999</v>
+      </c>
+      <c r="O84">
+        <v>0.11107709</v>
+      </c>
+      <c r="P84">
+        <v>0.7775396299999999</v>
+      </c>
+      <c r="Q84">
+        <v>1.04053963</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2584186315709767</v>
+      </c>
+      <c r="T84">
+        <v>4.010090383007396</v>
+      </c>
+      <c r="U84">
+        <v>0.0447</v>
+      </c>
+      <c r="V84">
+        <v>0.125</v>
+      </c>
+      <c r="W84">
+        <v>0.0391125</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>19.36619427207084</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.07853567108711733</v>
+      </c>
+      <c r="C85">
+        <v>0.2535165250742368</v>
+      </c>
+      <c r="D85">
+        <v>1.169116525074237</v>
+      </c>
+      <c r="E85">
+        <v>1.0956</v>
+      </c>
+      <c r="F85">
+        <v>1.0956</v>
+      </c>
+      <c r="G85">
+        <v>0.18</v>
+      </c>
+      <c r="H85">
+        <v>1.32</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.2</v>
+      </c>
+      <c r="K85">
+        <v>0.263</v>
+      </c>
+      <c r="L85">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M85">
+        <v>0.04897332000000001</v>
+      </c>
+      <c r="N85">
+        <v>0.88802668</v>
+      </c>
+      <c r="O85">
+        <v>0.111003335</v>
+      </c>
+      <c r="P85">
+        <v>0.7770233449999999</v>
+      </c>
+      <c r="Q85">
+        <v>1.040023345</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2710135063948079</v>
+      </c>
+      <c r="T85">
+        <v>4.240064434138412</v>
+      </c>
+      <c r="U85">
+        <v>0.0447</v>
+      </c>
+      <c r="V85">
+        <v>0.125</v>
+      </c>
+      <c r="W85">
+        <v>0.0391125</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>19.13286663023867</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.07848373849145887</v>
+      </c>
+      <c r="C86">
+        <v>0.2406763970763421</v>
+      </c>
+      <c r="D86">
+        <v>1.169476397076342</v>
+      </c>
+      <c r="E86">
+        <v>1.1088</v>
+      </c>
+      <c r="F86">
+        <v>1.1088</v>
+      </c>
+      <c r="G86">
+        <v>0.18</v>
+      </c>
+      <c r="H86">
+        <v>1.32</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.2</v>
+      </c>
+      <c r="K86">
+        <v>0.263</v>
+      </c>
+      <c r="L86">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M86">
+        <v>0.04956336000000001</v>
+      </c>
+      <c r="N86">
+        <v>0.8874366399999999</v>
+      </c>
+      <c r="O86">
+        <v>0.11092958</v>
+      </c>
+      <c r="P86">
+        <v>0.7765070599999999</v>
+      </c>
+      <c r="Q86">
+        <v>1.03950706</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2851827405716179</v>
+      </c>
+      <c r="T86">
+        <v>4.498785241660801</v>
+      </c>
+      <c r="U86">
+        <v>0.0447</v>
+      </c>
+      <c r="V86">
+        <v>0.125</v>
+      </c>
+      <c r="W86">
+        <v>0.0391125</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>18.90509440845011</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.0784318058958004</v>
+      </c>
+      <c r="C87">
+        <v>0.2278364906949106</v>
+      </c>
+      <c r="D87">
+        <v>1.169836490694911</v>
+      </c>
+      <c r="E87">
+        <v>1.122</v>
+      </c>
+      <c r="F87">
+        <v>1.122</v>
+      </c>
+      <c r="G87">
+        <v>0.18</v>
+      </c>
+      <c r="H87">
+        <v>1.32</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.2</v>
+      </c>
+      <c r="K87">
+        <v>0.263</v>
+      </c>
+      <c r="L87">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M87">
+        <v>0.05015340000000001</v>
+      </c>
+      <c r="N87">
+        <v>0.8868465999999999</v>
+      </c>
+      <c r="O87">
+        <v>0.110855825</v>
+      </c>
+      <c r="P87">
+        <v>0.7759907749999999</v>
+      </c>
+      <c r="Q87">
+        <v>1.038990775</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3012412059720026</v>
+      </c>
+      <c r="T87">
+        <v>4.792002156852846</v>
+      </c>
+      <c r="U87">
+        <v>0.0447</v>
+      </c>
+      <c r="V87">
+        <v>0.125</v>
+      </c>
+      <c r="W87">
+        <v>0.0391125</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>18.68268153305658</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.07837987330014194</v>
+      </c>
+      <c r="C88">
+        <v>0.2149968061347196</v>
+      </c>
+      <c r="D88">
+        <v>1.17019680613472</v>
+      </c>
+      <c r="E88">
+        <v>1.1352</v>
+      </c>
+      <c r="F88">
+        <v>1.1352</v>
+      </c>
+      <c r="G88">
+        <v>0.18</v>
+      </c>
+      <c r="H88">
+        <v>1.32</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.2</v>
+      </c>
+      <c r="K88">
+        <v>0.263</v>
+      </c>
+      <c r="L88">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M88">
+        <v>0.05074344</v>
+      </c>
+      <c r="N88">
+        <v>0.88625656</v>
+      </c>
+      <c r="O88">
+        <v>0.11078207</v>
+      </c>
+      <c r="P88">
+        <v>0.77547449</v>
+      </c>
+      <c r="Q88">
+        <v>1.03847449</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3195937378581567</v>
+      </c>
+      <c r="T88">
+        <v>5.127107202786613</v>
+      </c>
+      <c r="U88">
+        <v>0.0447</v>
+      </c>
+      <c r="V88">
+        <v>0.125</v>
+      </c>
+      <c r="W88">
+        <v>0.0391125</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>18.46544105011406</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.07832794070448347</v>
+      </c>
+      <c r="C89">
+        <v>0.2021573436007975</v>
+      </c>
+      <c r="D89">
+        <v>1.170557343600798</v>
+      </c>
+      <c r="E89">
+        <v>1.1484</v>
+      </c>
+      <c r="F89">
+        <v>1.1484</v>
+      </c>
+      <c r="G89">
+        <v>0.18</v>
+      </c>
+      <c r="H89">
+        <v>1.32</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.2</v>
+      </c>
+      <c r="K89">
+        <v>0.263</v>
+      </c>
+      <c r="L89">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M89">
+        <v>0.05133348000000001</v>
+      </c>
+      <c r="N89">
+        <v>0.8856665199999999</v>
+      </c>
+      <c r="O89">
+        <v>0.110708315</v>
+      </c>
+      <c r="P89">
+        <v>0.7749582049999999</v>
+      </c>
+      <c r="Q89">
+        <v>1.037958205</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3407697361883344</v>
+      </c>
+      <c r="T89">
+        <v>5.513766871171726</v>
+      </c>
+      <c r="U89">
+        <v>0.0447</v>
+      </c>
+      <c r="V89">
+        <v>0.125</v>
+      </c>
+      <c r="W89">
+        <v>0.0391125</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>18.25319460126217</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.07827600810882501</v>
+      </c>
+      <c r="C90">
+        <v>0.1893181032984268</v>
+      </c>
+      <c r="D90">
+        <v>1.170918103298427</v>
+      </c>
+      <c r="E90">
+        <v>1.1616</v>
+      </c>
+      <c r="F90">
+        <v>1.1616</v>
+      </c>
+      <c r="G90">
+        <v>0.18</v>
+      </c>
+      <c r="H90">
+        <v>1.32</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.2</v>
+      </c>
+      <c r="K90">
+        <v>0.263</v>
+      </c>
+      <c r="L90">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M90">
+        <v>0.05192352</v>
+      </c>
+      <c r="N90">
+        <v>0.8850764799999999</v>
+      </c>
+      <c r="O90">
+        <v>0.11063456</v>
+      </c>
+      <c r="P90">
+        <v>0.7744419199999999</v>
+      </c>
+      <c r="Q90">
+        <v>1.03744192</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3654750675735418</v>
+      </c>
+      <c r="T90">
+        <v>5.964869817621026</v>
+      </c>
+      <c r="U90">
+        <v>0.0447</v>
+      </c>
+      <c r="V90">
+        <v>0.125</v>
+      </c>
+      <c r="W90">
+        <v>0.0391125</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>18.04577193533874</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.07822407551316654</v>
+      </c>
+      <c r="C91">
+        <v>0.1764790854331428</v>
+      </c>
+      <c r="D91">
+        <v>1.171279085433143</v>
+      </c>
+      <c r="E91">
+        <v>1.1748</v>
+      </c>
+      <c r="F91">
+        <v>1.1748</v>
+      </c>
+      <c r="G91">
+        <v>0.18</v>
+      </c>
+      <c r="H91">
+        <v>1.32</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.2</v>
+      </c>
+      <c r="K91">
+        <v>0.263</v>
+      </c>
+      <c r="L91">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M91">
+        <v>0.05251356000000001</v>
+      </c>
+      <c r="N91">
+        <v>0.88448644</v>
+      </c>
+      <c r="O91">
+        <v>0.110560805</v>
+      </c>
+      <c r="P91">
+        <v>0.773925635</v>
+      </c>
+      <c r="Q91">
+        <v>1.036925635</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3946722773924232</v>
+      </c>
+      <c r="T91">
+        <v>6.497991481606562</v>
+      </c>
+      <c r="U91">
+        <v>0.0447</v>
+      </c>
+      <c r="V91">
+        <v>0.125</v>
+      </c>
+      <c r="W91">
+        <v>0.0391125</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>17.84301045291921</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.07817214291750808</v>
+      </c>
+      <c r="C92">
+        <v>0.1636402902107339</v>
+      </c>
+      <c r="D92">
+        <v>1.171640290210734</v>
+      </c>
+      <c r="E92">
+        <v>1.188</v>
+      </c>
+      <c r="F92">
+        <v>1.188</v>
+      </c>
+      <c r="G92">
+        <v>0.18</v>
+      </c>
+      <c r="H92">
+        <v>1.32</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.2</v>
+      </c>
+      <c r="K92">
+        <v>0.263</v>
+      </c>
+      <c r="L92">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M92">
+        <v>0.05310360000000001</v>
+      </c>
+      <c r="N92">
+        <v>0.8838963999999999</v>
+      </c>
+      <c r="O92">
+        <v>0.11048705</v>
+      </c>
+      <c r="P92">
+        <v>0.7734093499999999</v>
+      </c>
+      <c r="Q92">
+        <v>1.03640935</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4297089291750809</v>
+      </c>
+      <c r="T92">
+        <v>7.137737478389207</v>
+      </c>
+      <c r="U92">
+        <v>0.0447</v>
+      </c>
+      <c r="V92">
+        <v>0.125</v>
+      </c>
+      <c r="W92">
+        <v>0.0391125</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>17.6447547812201</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.07812021032184963</v>
+      </c>
+      <c r="C93">
+        <v>0.1508017178372434</v>
+      </c>
+      <c r="D93">
+        <v>1.172001717837243</v>
+      </c>
+      <c r="E93">
+        <v>1.2012</v>
+      </c>
+      <c r="F93">
+        <v>1.2012</v>
+      </c>
+      <c r="G93">
+        <v>0.18</v>
+      </c>
+      <c r="H93">
+        <v>1.32</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.2</v>
+      </c>
+      <c r="K93">
+        <v>0.263</v>
+      </c>
+      <c r="L93">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M93">
+        <v>0.05369364000000001</v>
+      </c>
+      <c r="N93">
+        <v>0.88330636</v>
+      </c>
+      <c r="O93">
+        <v>0.110413295</v>
+      </c>
+      <c r="P93">
+        <v>0.772893065</v>
+      </c>
+      <c r="Q93">
+        <v>1.035893065</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.472531503576107</v>
+      </c>
+      <c r="T93">
+        <v>7.91964925223466</v>
+      </c>
+      <c r="U93">
+        <v>0.0447</v>
+      </c>
+      <c r="V93">
+        <v>0.125</v>
+      </c>
+      <c r="W93">
+        <v>0.0391125</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>17.45085637703087</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.07806827772619118</v>
+      </c>
+      <c r="C94">
+        <v>0.1379633685189672</v>
+      </c>
+      <c r="D94">
+        <v>1.172363368518967</v>
+      </c>
+      <c r="E94">
+        <v>1.2144</v>
+      </c>
+      <c r="F94">
+        <v>1.2144</v>
+      </c>
+      <c r="G94">
+        <v>0.18</v>
+      </c>
+      <c r="H94">
+        <v>1.32</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.2</v>
+      </c>
+      <c r="K94">
+        <v>0.263</v>
+      </c>
+      <c r="L94">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M94">
+        <v>0.05428368000000001</v>
+      </c>
+      <c r="N94">
+        <v>0.8827163199999999</v>
+      </c>
+      <c r="O94">
+        <v>0.11033954</v>
+      </c>
+      <c r="P94">
+        <v>0.7723767799999999</v>
+      </c>
+      <c r="Q94">
+        <v>1.03537678</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5260597215773899</v>
+      </c>
+      <c r="T94">
+        <v>8.89703896954148</v>
+      </c>
+      <c r="U94">
+        <v>0.0447</v>
+      </c>
+      <c r="V94">
+        <v>0.125</v>
+      </c>
+      <c r="W94">
+        <v>0.0391125</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>17.2611731555414</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.07801634513053271</v>
+      </c>
+      <c r="C95">
+        <v>0.1251252424624583</v>
+      </c>
+      <c r="D95">
+        <v>1.172725242462458</v>
+      </c>
+      <c r="E95">
+        <v>1.2276</v>
+      </c>
+      <c r="F95">
+        <v>1.2276</v>
+      </c>
+      <c r="G95">
+        <v>0.18</v>
+      </c>
+      <c r="H95">
+        <v>1.32</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.2</v>
+      </c>
+      <c r="K95">
+        <v>0.263</v>
+      </c>
+      <c r="L95">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M95">
+        <v>0.05487372000000001</v>
+      </c>
+      <c r="N95">
+        <v>0.8821262799999999</v>
+      </c>
+      <c r="O95">
+        <v>0.110265785</v>
+      </c>
+      <c r="P95">
+        <v>0.771860495</v>
+      </c>
+      <c r="Q95">
+        <v>1.034860495</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5948817161504676</v>
+      </c>
+      <c r="T95">
+        <v>10.1536828917931</v>
+      </c>
+      <c r="U95">
+        <v>0.0447</v>
+      </c>
+      <c r="V95">
+        <v>0.125</v>
+      </c>
+      <c r="W95">
+        <v>0.0391125</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>17.07556914311623</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.07796441253487424</v>
+      </c>
+      <c r="C96">
+        <v>0.1122873398745223</v>
+      </c>
+      <c r="D96">
+        <v>1.173087339874523</v>
+      </c>
+      <c r="E96">
+        <v>1.2408</v>
+      </c>
+      <c r="F96">
+        <v>1.2408</v>
+      </c>
+      <c r="G96">
+        <v>0.18</v>
+      </c>
+      <c r="H96">
+        <v>1.32</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.2</v>
+      </c>
+      <c r="K96">
+        <v>0.263</v>
+      </c>
+      <c r="L96">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M96">
+        <v>0.05546376000000001</v>
+      </c>
+      <c r="N96">
+        <v>0.88153624</v>
+      </c>
+      <c r="O96">
+        <v>0.11019203</v>
+      </c>
+      <c r="P96">
+        <v>0.77134421</v>
+      </c>
+      <c r="Q96">
+        <v>1.03434421</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6866443755812379</v>
+      </c>
+      <c r="T96">
+        <v>11.82920812146193</v>
+      </c>
+      <c r="U96">
+        <v>0.0447</v>
+      </c>
+      <c r="V96">
+        <v>0.125</v>
+      </c>
+      <c r="W96">
+        <v>0.0391125</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>16.89391415223201</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.07791247993921578</v>
+      </c>
+      <c r="C97">
+        <v>0.09944966096222196</v>
+      </c>
+      <c r="D97">
+        <v>1.173449660962222</v>
+      </c>
+      <c r="E97">
+        <v>1.254</v>
+      </c>
+      <c r="F97">
+        <v>1.254</v>
+      </c>
+      <c r="G97">
+        <v>0.18</v>
+      </c>
+      <c r="H97">
+        <v>1.32</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.2</v>
+      </c>
+      <c r="K97">
+        <v>0.263</v>
+      </c>
+      <c r="L97">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M97">
+        <v>0.05605380000000001</v>
+      </c>
+      <c r="N97">
+        <v>0.8809461999999999</v>
+      </c>
+      <c r="O97">
+        <v>0.110118275</v>
+      </c>
+      <c r="P97">
+        <v>0.7708279249999999</v>
+      </c>
+      <c r="Q97">
+        <v>1.033827925</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8151120987843166</v>
+      </c>
+      <c r="T97">
+        <v>14.1749434429983</v>
+      </c>
+      <c r="U97">
+        <v>0.0447</v>
+      </c>
+      <c r="V97">
+        <v>0.125</v>
+      </c>
+      <c r="W97">
+        <v>0.0391125</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>16.71608347694536</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.07786054734355732</v>
+      </c>
+      <c r="C98">
+        <v>0.08661220593287555</v>
+      </c>
+      <c r="D98">
+        <v>1.173812205932876</v>
+      </c>
+      <c r="E98">
+        <v>1.2672</v>
+      </c>
+      <c r="F98">
+        <v>1.2672</v>
+      </c>
+      <c r="G98">
+        <v>0.18</v>
+      </c>
+      <c r="H98">
+        <v>1.32</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.2</v>
+      </c>
+      <c r="K98">
+        <v>0.263</v>
+      </c>
+      <c r="L98">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M98">
+        <v>0.05664384000000001</v>
+      </c>
+      <c r="N98">
+        <v>0.8803561599999999</v>
+      </c>
+      <c r="O98">
+        <v>0.11004452</v>
+      </c>
+      <c r="P98">
+        <v>0.77031164</v>
+      </c>
+      <c r="Q98">
+        <v>1.03331164</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.007813683588932</v>
+      </c>
+      <c r="T98">
+        <v>17.69354642530281</v>
+      </c>
+      <c r="U98">
+        <v>0.0447</v>
+      </c>
+      <c r="V98">
+        <v>0.125</v>
+      </c>
+      <c r="W98">
+        <v>0.0391125</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>16.54195760739385</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.07780861474789885</v>
+      </c>
+      <c r="C99">
+        <v>0.07377497499405727</v>
+      </c>
+      <c r="D99">
+        <v>1.174174974994057</v>
+      </c>
+      <c r="E99">
+        <v>1.2804</v>
+      </c>
+      <c r="F99">
+        <v>1.2804</v>
+      </c>
+      <c r="G99">
+        <v>0.18</v>
+      </c>
+      <c r="H99">
+        <v>1.32</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.2</v>
+      </c>
+      <c r="K99">
+        <v>0.263</v>
+      </c>
+      <c r="L99">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M99">
+        <v>0.05723388</v>
+      </c>
+      <c r="N99">
+        <v>0.87976612</v>
+      </c>
+      <c r="O99">
+        <v>0.109970765</v>
+      </c>
+      <c r="P99">
+        <v>0.769795355</v>
+      </c>
+      <c r="Q99">
+        <v>1.032795355</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.328982991596627</v>
+      </c>
+      <c r="T99">
+        <v>23.5578847291437</v>
+      </c>
+      <c r="U99">
+        <v>0.0447</v>
+      </c>
+      <c r="V99">
+        <v>0.125</v>
+      </c>
+      <c r="W99">
+        <v>0.0391125</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>16.3714219619568</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.07775668215224039</v>
+      </c>
+      <c r="C100">
+        <v>0.06093796835359822</v>
+      </c>
+      <c r="D100">
+        <v>1.174537968353598</v>
+      </c>
+      <c r="E100">
+        <v>1.2936</v>
+      </c>
+      <c r="F100">
+        <v>1.2936</v>
+      </c>
+      <c r="G100">
+        <v>0.18</v>
+      </c>
+      <c r="H100">
+        <v>1.32</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.2</v>
+      </c>
+      <c r="K100">
+        <v>0.263</v>
+      </c>
+      <c r="L100">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M100">
+        <v>0.05782392000000001</v>
+      </c>
+      <c r="N100">
+        <v>0.8791760799999999</v>
+      </c>
+      <c r="O100">
+        <v>0.10989701</v>
+      </c>
+      <c r="P100">
+        <v>0.76927907</v>
+      </c>
+      <c r="Q100">
+        <v>1.03227907</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.971321607612018</v>
+      </c>
+      <c r="T100">
+        <v>35.28656133682548</v>
+      </c>
+      <c r="U100">
+        <v>0.0447</v>
+      </c>
+      <c r="V100">
+        <v>0.125</v>
+      </c>
+      <c r="W100">
+        <v>0.0391125</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>16.20436663581438</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.07770474955658194</v>
+      </c>
+      <c r="C101">
+        <v>0.04810118621958703</v>
+      </c>
+      <c r="D101">
+        <v>1.174901186219587</v>
+      </c>
+      <c r="E101">
+        <v>1.3068</v>
+      </c>
+      <c r="F101">
+        <v>1.3068</v>
+      </c>
+      <c r="G101">
+        <v>0.18</v>
+      </c>
+      <c r="H101">
+        <v>1.32</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.2</v>
+      </c>
+      <c r="K101">
+        <v>0.263</v>
+      </c>
+      <c r="L101">
+        <v>0.9369999999999999</v>
+      </c>
+      <c r="M101">
+        <v>0.05841396</v>
+      </c>
+      <c r="N101">
+        <v>0.87858604</v>
+      </c>
+      <c r="O101">
+        <v>0.109823255</v>
+      </c>
+      <c r="P101">
+        <v>0.7687627849999999</v>
+      </c>
+      <c r="Q101">
+        <v>1.031762785</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.89833745565819</v>
+      </c>
+      <c r="T101">
+        <v>70.47259115987083</v>
+      </c>
+      <c r="U101">
+        <v>0.0447</v>
+      </c>
+      <c r="V101">
+        <v>0.125</v>
+      </c>
+      <c r="W101">
+        <v>0.0391125</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>16.04068616474555</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
